--- a/cfdata.xlsx
+++ b/cfdata.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16110" windowHeight="12975"/>
+    <workbookView windowWidth="27930" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
   <si>
     <t>采样地点</t>
   </si>
@@ -59,10 +60,208 @@
     <t>12802采空区</t>
   </si>
   <si>
+    <t>2026-09-06 00:16:28</t>
+  </si>
+  <si>
+    <t>2026-09-06 00:40:36</t>
+  </si>
+  <si>
+    <t>2026-09-06 01:04:44</t>
+  </si>
+  <si>
+    <t>2026-09-06 01:28:54</t>
+  </si>
+  <si>
+    <t>2026-09-06 01:53:02</t>
+  </si>
+  <si>
+    <t>2026-09-06 02:17:10</t>
+  </si>
+  <si>
+    <t>2026-09-06 02:41:19</t>
+  </si>
+  <si>
+    <t>2026-09-06 03:05:28</t>
+  </si>
+  <si>
+    <t>2026-09-06 03:29:36</t>
+  </si>
+  <si>
+    <t>2026-09-06 03:53:45</t>
+  </si>
+  <si>
+    <t>2026-09-06 04:17:55</t>
+  </si>
+  <si>
+    <t>2026-09-06 04:42:04</t>
+  </si>
+  <si>
+    <t>2026-09-06 05:06:13</t>
+  </si>
+  <si>
+    <t>2026-09-06 05:30:22</t>
+  </si>
+  <si>
+    <t>2026-09-06 05:54:32</t>
+  </si>
+  <si>
+    <t>2026-09-06 06:18:40</t>
+  </si>
+  <si>
+    <t>2026-09-06 06:42:49</t>
+  </si>
+  <si>
+    <t>2026-09-06 07:06:59</t>
+  </si>
+  <si>
+    <t>2026-09-06 07:47:03</t>
+  </si>
+  <si>
+    <t>2026-09-06 08:11:11</t>
+  </si>
+  <si>
+    <t>2026-09-06 08:35:18</t>
+  </si>
+  <si>
+    <t>2026-09-06 08:59:26</t>
+  </si>
+  <si>
+    <t>12803采空区（回风巷）</t>
+  </si>
+  <si>
+    <t>2026-09-06 00:24:30</t>
+  </si>
+  <si>
+    <t>2026-09-06 00:48:39</t>
+  </si>
+  <si>
+    <t>2026-09-06 01:12:47</t>
+  </si>
+  <si>
+    <t>2026-09-06 01:36:56</t>
+  </si>
+  <si>
+    <t>2026-09-06 02:01:05</t>
+  </si>
+  <si>
+    <t>2026-09-06 02:25:13</t>
+  </si>
+  <si>
+    <t>2026-09-06 02:49:22</t>
+  </si>
+  <si>
+    <t>2026-09-06 03:13:31</t>
+  </si>
+  <si>
+    <t>2026-09-06 04:01:48</t>
+  </si>
+  <si>
+    <t>2026-09-06 04:25:58</t>
+  </si>
+  <si>
+    <t>2026-09-06 04:50:07</t>
+  </si>
+  <si>
+    <t>2026-09-06 05:14:16</t>
+  </si>
+  <si>
+    <t>2026-09-06 05:38:25</t>
+  </si>
+  <si>
+    <t>2026-09-06 06:02:34</t>
+  </si>
+  <si>
+    <t>2026-09-06 06:26:43</t>
+  </si>
+  <si>
+    <t>2026-09-06 06:50:52</t>
+  </si>
+  <si>
+    <t>2026-09-06 07:15:01</t>
+  </si>
+  <si>
+    <t>2026-09-06 07:55:06</t>
+  </si>
+  <si>
+    <t>2026-09-06 08:19:13</t>
+  </si>
+  <si>
+    <t>2026-09-06 08:43:21</t>
+  </si>
+  <si>
+    <t>2026-09-06 09:07:28</t>
+  </si>
+  <si>
+    <t>12803采空区（运输巷）</t>
+  </si>
+  <si>
+    <t>2026-09-06 00:32:33</t>
+  </si>
+  <si>
+    <t>2026-09-06 00:56:41</t>
+  </si>
+  <si>
+    <t>2026-09-06 01:20:50</t>
+  </si>
+  <si>
+    <t>2026-09-06 01:44:59</t>
+  </si>
+  <si>
+    <t>2026-09-06 02:09:08</t>
+  </si>
+  <si>
+    <t>2026-09-06 02:33:16</t>
+  </si>
+  <si>
+    <t>2026-09-06 02:57:25</t>
+  </si>
+  <si>
+    <t>2026-09-06 03:21:33</t>
+  </si>
+  <si>
+    <t>2026-09-06 03:45:42</t>
+  </si>
+  <si>
+    <t>2026-09-06 04:09:51</t>
+  </si>
+  <si>
+    <t>2026-09-06 04:34:01</t>
+  </si>
+  <si>
+    <t>2026-09-06 04:58:10</t>
+  </si>
+  <si>
+    <t>2026-09-06 05:22:18</t>
+  </si>
+  <si>
+    <t>2026-09-06 05:46:28</t>
+  </si>
+  <si>
+    <t>2026-09-06 06:10:37</t>
+  </si>
+  <si>
+    <t>2026-09-06 06:34:46</t>
+  </si>
+  <si>
+    <t>2026-09-06 06:58:55</t>
+  </si>
+  <si>
+    <t>2026-09-06 07:23:05</t>
+  </si>
+  <si>
+    <t>2026-09-06 08:03:08</t>
+  </si>
+  <si>
+    <t>2026-09-06 08:27:16</t>
+  </si>
+  <si>
+    <t>2026-09-06 08:51:24</t>
+  </si>
+  <si>
+    <t>2026-09-06 09:15:31</t>
+  </si>
+  <si>
     <t>12803采空区（运输巷)</t>
-  </si>
-  <si>
-    <t>12803采空区（回风巷）</t>
   </si>
   <si>
     <t xml:space="preserve">81 27135 </t>
@@ -86,7 +285,7 @@
     <numFmt numFmtId="179" formatCode="0.0_ "/>
     <numFmt numFmtId="180" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +310,13 @@
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -452,7 +658,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -524,6 +730,30 @@
       <top/>
       <bottom style="medium">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,137 +875,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -834,6 +1064,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="180" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -888,7 +1133,17 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1082,25 +1337,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1361,6 +1616,2177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:J67"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="23.575" customWidth="1"/>
+    <col min="2" max="2" width="24.125" customWidth="1"/>
+    <col min="3" max="3" width="11.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="6" max="6" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="11.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25" spans="1:10">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:10">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="22">
+        <v>80.79627</v>
+      </c>
+      <c r="D2" s="22">
+        <v>0.34175</v>
+      </c>
+      <c r="E2" s="23">
+        <v>0</v>
+      </c>
+      <c r="F2" s="22">
+        <v>18.83142</v>
+      </c>
+      <c r="G2" s="23">
+        <v>0</v>
+      </c>
+      <c r="H2" s="23">
+        <v>4.3</v>
+      </c>
+      <c r="I2" s="23">
+        <v>0</v>
+      </c>
+      <c r="J2" s="22">
+        <v>0.03013</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:10">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="22">
+        <v>80.85424</v>
+      </c>
+      <c r="D3" s="22">
+        <v>0.33417</v>
+      </c>
+      <c r="E3" s="23">
+        <v>0</v>
+      </c>
+      <c r="F3" s="22">
+        <v>18.78116</v>
+      </c>
+      <c r="G3" s="23">
+        <v>0</v>
+      </c>
+      <c r="H3" s="23">
+        <v>14.9</v>
+      </c>
+      <c r="I3" s="23">
+        <v>0</v>
+      </c>
+      <c r="J3" s="22">
+        <v>0.02895</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:10">
+      <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="22">
+        <v>80.8857</v>
+      </c>
+      <c r="D4" s="22">
+        <v>0.33517</v>
+      </c>
+      <c r="E4" s="23">
+        <v>0</v>
+      </c>
+      <c r="F4" s="22">
+        <v>18.75573</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0</v>
+      </c>
+      <c r="H4" s="23">
+        <v>14.3</v>
+      </c>
+      <c r="I4" s="23">
+        <v>0</v>
+      </c>
+      <c r="J4" s="22">
+        <v>0.02197</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:10">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="22">
+        <v>80.88314</v>
+      </c>
+      <c r="D5" s="22">
+        <v>0.33665</v>
+      </c>
+      <c r="E5" s="23">
+        <v>0</v>
+      </c>
+      <c r="F5" s="22">
+        <v>18.75208</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>11.8</v>
+      </c>
+      <c r="I5" s="23">
+        <v>0</v>
+      </c>
+      <c r="J5" s="22">
+        <v>0.02694</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:10">
+      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="22">
+        <v>80.85319</v>
+      </c>
+      <c r="D6" s="22">
+        <v>0.34062</v>
+      </c>
+      <c r="E6" s="23">
+        <v>0</v>
+      </c>
+      <c r="F6" s="22">
+        <v>18.77323</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23">
+        <v>16.8</v>
+      </c>
+      <c r="I6" s="23">
+        <v>0</v>
+      </c>
+      <c r="J6" s="22">
+        <v>0.03128</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:10">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="22">
+        <v>80.8053</v>
+      </c>
+      <c r="D7" s="22">
+        <v>0.3439</v>
+      </c>
+      <c r="E7" s="23">
+        <v>0</v>
+      </c>
+      <c r="F7" s="22">
+        <v>18.79347</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23">
+        <v>5.3</v>
+      </c>
+      <c r="I7" s="23">
+        <v>0</v>
+      </c>
+      <c r="J7" s="22">
+        <v>0.0568</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:10">
+      <c r="A8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="22">
+        <v>80.79943</v>
+      </c>
+      <c r="D8" s="22">
+        <v>0.34051</v>
+      </c>
+      <c r="E8" s="23">
+        <v>0</v>
+      </c>
+      <c r="F8" s="22">
+        <v>18.78527</v>
+      </c>
+      <c r="G8" s="23">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23">
+        <v>12.5</v>
+      </c>
+      <c r="I8" s="23">
+        <v>0</v>
+      </c>
+      <c r="J8" s="22">
+        <v>0.07354</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:10">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="22">
+        <v>80.96898</v>
+      </c>
+      <c r="D9" s="22">
+        <v>0.3352</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0</v>
+      </c>
+      <c r="F9" s="22">
+        <v>18.62333</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>8.3</v>
+      </c>
+      <c r="I9" s="23">
+        <v>0</v>
+      </c>
+      <c r="J9" s="22">
+        <v>0.07165</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:10">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="22">
+        <v>80.9102</v>
+      </c>
+      <c r="D10" s="22">
+        <v>0.343</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0</v>
+      </c>
+      <c r="F10" s="22">
+        <v>18.67779</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23">
+        <v>15.2</v>
+      </c>
+      <c r="I10" s="23">
+        <v>0</v>
+      </c>
+      <c r="J10" s="22">
+        <v>0.06749</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:10">
+      <c r="A11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="22">
+        <v>80.90591</v>
+      </c>
+      <c r="D11" s="22">
+        <v>0.34244</v>
+      </c>
+      <c r="E11" s="23">
+        <v>0</v>
+      </c>
+      <c r="F11" s="22">
+        <v>18.68527</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0</v>
+      </c>
+      <c r="H11" s="23">
+        <v>11.2</v>
+      </c>
+      <c r="I11" s="23">
+        <v>0</v>
+      </c>
+      <c r="J11" s="22">
+        <v>0.06527</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:10">
+      <c r="A12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="22">
+        <v>80.91769</v>
+      </c>
+      <c r="D12" s="22">
+        <v>0.34597</v>
+      </c>
+      <c r="E12" s="23">
+        <v>0</v>
+      </c>
+      <c r="F12" s="22">
+        <v>18.65389</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>19.2</v>
+      </c>
+      <c r="I12" s="23">
+        <v>0</v>
+      </c>
+      <c r="J12" s="22">
+        <v>0.08052</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:10">
+      <c r="A13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="22">
+        <v>80.91144</v>
+      </c>
+      <c r="D13" s="22">
+        <v>0.34487</v>
+      </c>
+      <c r="E13" s="23">
+        <v>0</v>
+      </c>
+      <c r="F13" s="22">
+        <v>18.64219</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>25.5</v>
+      </c>
+      <c r="I13" s="23">
+        <v>0</v>
+      </c>
+      <c r="J13" s="22">
+        <v>0.09896</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:10">
+      <c r="A14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="22">
+        <v>80.86653</v>
+      </c>
+      <c r="D14" s="22">
+        <v>0.35097</v>
+      </c>
+      <c r="E14" s="23">
+        <v>0</v>
+      </c>
+      <c r="F14" s="22">
+        <v>18.67212</v>
+      </c>
+      <c r="G14" s="23">
+        <v>0</v>
+      </c>
+      <c r="H14" s="23">
+        <v>5.4</v>
+      </c>
+      <c r="I14" s="23">
+        <v>0</v>
+      </c>
+      <c r="J14" s="22">
+        <v>0.10983</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:10">
+      <c r="A15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="22">
+        <v>80.86792</v>
+      </c>
+      <c r="D15" s="22">
+        <v>0.35271</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="22">
+        <v>18.65852</v>
+      </c>
+      <c r="G15" s="23">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23">
+        <v>4.8</v>
+      </c>
+      <c r="I15" s="23">
+        <v>0</v>
+      </c>
+      <c r="J15" s="22">
+        <v>0.12037</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:10">
+      <c r="A16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="22">
+        <v>80.85043</v>
+      </c>
+      <c r="D16" s="22">
+        <v>0.34908</v>
+      </c>
+      <c r="E16" s="23">
+        <v>0</v>
+      </c>
+      <c r="F16" s="22">
+        <v>18.63952</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>0</v>
+      </c>
+      <c r="I16" s="23">
+        <v>0</v>
+      </c>
+      <c r="J16" s="22">
+        <v>0.16098</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:10">
+      <c r="A17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="22">
+        <v>80.77438</v>
+      </c>
+      <c r="D17" s="22">
+        <v>0.35363</v>
+      </c>
+      <c r="E17" s="23">
+        <v>0</v>
+      </c>
+      <c r="F17" s="22">
+        <v>18.67809</v>
+      </c>
+      <c r="G17" s="23">
+        <v>0</v>
+      </c>
+      <c r="H17" s="23">
+        <v>7.2</v>
+      </c>
+      <c r="I17" s="23">
+        <v>0</v>
+      </c>
+      <c r="J17" s="22">
+        <v>0.19317</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:10">
+      <c r="A18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="22">
+        <v>80.77319</v>
+      </c>
+      <c r="D18" s="22">
+        <v>0.35343</v>
+      </c>
+      <c r="E18" s="23">
+        <v>0</v>
+      </c>
+      <c r="F18" s="22">
+        <v>18.68369</v>
+      </c>
+      <c r="G18" s="23">
+        <v>0</v>
+      </c>
+      <c r="H18" s="23">
+        <v>22.5</v>
+      </c>
+      <c r="I18" s="23">
+        <v>0</v>
+      </c>
+      <c r="J18" s="22">
+        <v>0.18743</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:10">
+      <c r="A19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="22">
+        <v>80.7879</v>
+      </c>
+      <c r="D19" s="22">
+        <v>0.35352</v>
+      </c>
+      <c r="E19" s="23">
+        <v>0</v>
+      </c>
+      <c r="F19" s="22">
+        <v>18.65949</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>7.4</v>
+      </c>
+      <c r="I19" s="23">
+        <v>0</v>
+      </c>
+      <c r="J19" s="22">
+        <v>0.19834</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:10">
+      <c r="A20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="22">
+        <v>80.46644</v>
+      </c>
+      <c r="D20" s="22">
+        <v>0.35329</v>
+      </c>
+      <c r="E20" s="23">
+        <v>0</v>
+      </c>
+      <c r="F20" s="22">
+        <v>18.60611</v>
+      </c>
+      <c r="G20" s="23">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23">
+        <v>6.7</v>
+      </c>
+      <c r="I20" s="23">
+        <v>0</v>
+      </c>
+      <c r="J20" s="22">
+        <v>0.57349</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:10">
+      <c r="A21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="22">
+        <v>80.52477</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0.35306</v>
+      </c>
+      <c r="E21" s="23">
+        <v>0</v>
+      </c>
+      <c r="F21" s="22">
+        <v>18.69053</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23">
+        <v>0</v>
+      </c>
+      <c r="I21" s="23">
+        <v>0</v>
+      </c>
+      <c r="J21" s="22">
+        <v>0.43165</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:10">
+      <c r="A22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22">
+        <v>80.63069</v>
+      </c>
+      <c r="D22" s="22">
+        <v>0.3507</v>
+      </c>
+      <c r="E22" s="23">
+        <v>0</v>
+      </c>
+      <c r="F22" s="22">
+        <v>18.70007</v>
+      </c>
+      <c r="G22" s="23">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>3.6</v>
+      </c>
+      <c r="I22" s="23">
+        <v>0</v>
+      </c>
+      <c r="J22" s="22">
+        <v>0.31818</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:10">
+      <c r="A23" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="22">
+        <v>80.61491</v>
+      </c>
+      <c r="D23" s="22">
+        <v>0.34824</v>
+      </c>
+      <c r="E23" s="23">
+        <v>0</v>
+      </c>
+      <c r="F23" s="22">
+        <v>18.7584</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>4.6</v>
+      </c>
+      <c r="I23" s="23">
+        <v>0</v>
+      </c>
+      <c r="J23" s="22">
+        <v>0.27798</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:10">
+      <c r="A24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="22">
+        <v>81.99542</v>
+      </c>
+      <c r="D24" s="22">
+        <v>0.39205</v>
+      </c>
+      <c r="E24" s="23">
+        <v>0</v>
+      </c>
+      <c r="F24" s="22">
+        <v>17.56161</v>
+      </c>
+      <c r="G24" s="23">
+        <v>17.9</v>
+      </c>
+      <c r="H24" s="23">
+        <v>48</v>
+      </c>
+      <c r="I24" s="23">
+        <v>0</v>
+      </c>
+      <c r="J24" s="22">
+        <v>0.04434</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:10">
+      <c r="A25" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="22">
+        <v>82.08538</v>
+      </c>
+      <c r="D25" s="22">
+        <v>0.3996</v>
+      </c>
+      <c r="E25" s="23">
+        <v>0</v>
+      </c>
+      <c r="F25" s="22">
+        <v>17.46044</v>
+      </c>
+      <c r="G25" s="23">
+        <v>18.1</v>
+      </c>
+      <c r="H25" s="23">
+        <v>62.9</v>
+      </c>
+      <c r="I25" s="23">
+        <v>0</v>
+      </c>
+      <c r="J25" s="22">
+        <v>0.04647</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:10">
+      <c r="A26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="22">
+        <v>82.05372</v>
+      </c>
+      <c r="D26" s="22">
+        <v>0.41003</v>
+      </c>
+      <c r="E26" s="23">
+        <v>0</v>
+      </c>
+      <c r="F26" s="22">
+        <v>17.448</v>
+      </c>
+      <c r="G26" s="23">
+        <v>16.7</v>
+      </c>
+      <c r="H26" s="24">
+        <v>61</v>
+      </c>
+      <c r="I26" s="23">
+        <v>0</v>
+      </c>
+      <c r="J26" s="22">
+        <v>0.07048</v>
+      </c>
+    </row>
+    <row r="27" ht="15" spans="1:10">
+      <c r="A27" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="22">
+        <v>82.08195</v>
+      </c>
+      <c r="D27" s="22">
+        <v>0.40991</v>
+      </c>
+      <c r="E27" s="23">
+        <v>0</v>
+      </c>
+      <c r="F27" s="22">
+        <v>17.45259</v>
+      </c>
+      <c r="G27" s="23">
+        <v>17.4</v>
+      </c>
+      <c r="H27" s="23">
+        <v>63.4</v>
+      </c>
+      <c r="I27" s="23">
+        <v>0</v>
+      </c>
+      <c r="J27" s="22">
+        <v>0.04748</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:10">
+      <c r="A28" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="22">
+        <v>82.05914</v>
+      </c>
+      <c r="D28" s="22">
+        <v>0.41312</v>
+      </c>
+      <c r="E28" s="23">
+        <v>0</v>
+      </c>
+      <c r="F28" s="22">
+        <v>17.45248</v>
+      </c>
+      <c r="G28" s="23">
+        <v>17.9</v>
+      </c>
+      <c r="H28" s="23">
+        <v>60.1</v>
+      </c>
+      <c r="I28" s="23">
+        <v>0</v>
+      </c>
+      <c r="J28" s="22">
+        <v>0.06747</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:10">
+      <c r="A29" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="22">
+        <v>82.03971</v>
+      </c>
+      <c r="D29" s="22">
+        <v>0.41467</v>
+      </c>
+      <c r="E29" s="23">
+        <v>0</v>
+      </c>
+      <c r="F29" s="22">
+        <v>17.47815</v>
+      </c>
+      <c r="G29" s="23">
+        <v>17.9</v>
+      </c>
+      <c r="H29" s="23">
+        <v>61.1</v>
+      </c>
+      <c r="I29" s="23">
+        <v>0</v>
+      </c>
+      <c r="J29" s="22">
+        <v>0.05958</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="1:10">
+      <c r="A30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="22">
+        <v>82.02074</v>
+      </c>
+      <c r="D30" s="22">
+        <v>0.4145</v>
+      </c>
+      <c r="E30" s="23">
+        <v>0</v>
+      </c>
+      <c r="F30" s="22">
+        <v>17.48058</v>
+      </c>
+      <c r="G30" s="23">
+        <v>17.7</v>
+      </c>
+      <c r="H30" s="23">
+        <v>62.4</v>
+      </c>
+      <c r="I30" s="23">
+        <v>0</v>
+      </c>
+      <c r="J30" s="22">
+        <v>0.07618</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="1:10">
+      <c r="A31" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="22">
+        <v>82.00478</v>
+      </c>
+      <c r="D31" s="22">
+        <v>0.41738</v>
+      </c>
+      <c r="E31" s="23">
+        <v>0</v>
+      </c>
+      <c r="F31" s="22">
+        <v>17.4652</v>
+      </c>
+      <c r="G31" s="23">
+        <v>18.6</v>
+      </c>
+      <c r="H31" s="23">
+        <v>55.8</v>
+      </c>
+      <c r="I31" s="23">
+        <v>0</v>
+      </c>
+      <c r="J31" s="22">
+        <v>0.10519</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:10">
+      <c r="A32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="22">
+        <v>81.98119</v>
+      </c>
+      <c r="D32" s="22">
+        <v>0.42209</v>
+      </c>
+      <c r="E32" s="23">
+        <v>0</v>
+      </c>
+      <c r="F32" s="22">
+        <v>17.47438</v>
+      </c>
+      <c r="G32" s="23">
+        <v>18.6</v>
+      </c>
+      <c r="H32" s="23">
+        <v>54</v>
+      </c>
+      <c r="I32" s="23">
+        <v>0</v>
+      </c>
+      <c r="J32" s="22">
+        <v>0.11507</v>
+      </c>
+    </row>
+    <row r="33" ht="15" spans="1:10">
+      <c r="A33" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="22">
+        <v>82.05141</v>
+      </c>
+      <c r="D33" s="22">
+        <v>0.42515</v>
+      </c>
+      <c r="E33" s="23">
+        <v>0</v>
+      </c>
+      <c r="F33" s="22">
+        <v>17.41678</v>
+      </c>
+      <c r="G33" s="23">
+        <v>15.4</v>
+      </c>
+      <c r="H33" s="23">
+        <v>60.4</v>
+      </c>
+      <c r="I33" s="23">
+        <v>0</v>
+      </c>
+      <c r="J33" s="22">
+        <v>0.09907</v>
+      </c>
+    </row>
+    <row r="34" ht="15" spans="1:10">
+      <c r="A34" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="22">
+        <v>82.10519</v>
+      </c>
+      <c r="D34" s="22">
+        <v>0.42866</v>
+      </c>
+      <c r="E34" s="23">
+        <v>0</v>
+      </c>
+      <c r="F34" s="22">
+        <v>17.33673</v>
+      </c>
+      <c r="G34" s="23">
+        <v>16.8</v>
+      </c>
+      <c r="H34" s="23">
+        <v>63.7</v>
+      </c>
+      <c r="I34" s="23">
+        <v>0</v>
+      </c>
+      <c r="J34" s="22">
+        <v>0.12137</v>
+      </c>
+    </row>
+    <row r="35" ht="15" spans="1:10">
+      <c r="A35" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="22">
+        <v>82.03838</v>
+      </c>
+      <c r="D35" s="22">
+        <v>0.43886</v>
+      </c>
+      <c r="E35" s="23">
+        <v>0</v>
+      </c>
+      <c r="F35" s="22">
+        <v>17.32688</v>
+      </c>
+      <c r="G35" s="23">
+        <v>20.9</v>
+      </c>
+      <c r="H35" s="23">
+        <v>58.3</v>
+      </c>
+      <c r="I35" s="23">
+        <v>0</v>
+      </c>
+      <c r="J35" s="22">
+        <v>0.18795</v>
+      </c>
+    </row>
+    <row r="36" ht="15" spans="1:10">
+      <c r="A36" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="22">
+        <v>81.9981</v>
+      </c>
+      <c r="D36" s="22">
+        <v>0.44273</v>
+      </c>
+      <c r="E36" s="23">
+        <v>0</v>
+      </c>
+      <c r="F36" s="22">
+        <v>17.36938</v>
+      </c>
+      <c r="G36" s="23">
+        <v>17.7</v>
+      </c>
+      <c r="H36" s="23">
+        <v>53.8</v>
+      </c>
+      <c r="I36" s="23">
+        <v>0</v>
+      </c>
+      <c r="J36" s="22">
+        <v>0.18264</v>
+      </c>
+    </row>
+    <row r="37" ht="15" spans="1:10">
+      <c r="A37" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="22">
+        <v>81.99336</v>
+      </c>
+      <c r="D37" s="22">
+        <v>0.44352</v>
+      </c>
+      <c r="E37" s="23">
+        <v>0</v>
+      </c>
+      <c r="F37" s="22">
+        <v>17.35115</v>
+      </c>
+      <c r="G37" s="23">
+        <v>17.6</v>
+      </c>
+      <c r="H37" s="23">
+        <v>59.2</v>
+      </c>
+      <c r="I37" s="23">
+        <v>0</v>
+      </c>
+      <c r="J37" s="22">
+        <v>0.20429</v>
+      </c>
+    </row>
+    <row r="38" ht="15" spans="1:10">
+      <c r="A38" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="22">
+        <v>81.99844</v>
+      </c>
+      <c r="D38" s="22">
+        <v>0.45164</v>
+      </c>
+      <c r="E38" s="23">
+        <v>0</v>
+      </c>
+      <c r="F38" s="22">
+        <v>17.32853</v>
+      </c>
+      <c r="G38" s="24">
+        <v>17</v>
+      </c>
+      <c r="H38" s="23">
+        <v>57.3</v>
+      </c>
+      <c r="I38" s="23">
+        <v>0</v>
+      </c>
+      <c r="J38" s="22">
+        <v>0.21396</v>
+      </c>
+    </row>
+    <row r="39" ht="15" spans="1:10">
+      <c r="A39" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="22">
+        <v>81.96129</v>
+      </c>
+      <c r="D39" s="22">
+        <v>0.44445</v>
+      </c>
+      <c r="E39" s="23">
+        <v>0</v>
+      </c>
+      <c r="F39" s="22">
+        <v>17.35005</v>
+      </c>
+      <c r="G39" s="23">
+        <v>17.6</v>
+      </c>
+      <c r="H39" s="23">
+        <v>57.5</v>
+      </c>
+      <c r="I39" s="23">
+        <v>0</v>
+      </c>
+      <c r="J39" s="22">
+        <v>0.23671</v>
+      </c>
+    </row>
+    <row r="40" ht="15" spans="1:10">
+      <c r="A40" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="22">
+        <v>81.98632</v>
+      </c>
+      <c r="D40" s="22">
+        <v>0.45563</v>
+      </c>
+      <c r="E40" s="23">
+        <v>0</v>
+      </c>
+      <c r="F40" s="22">
+        <v>17.29155</v>
+      </c>
+      <c r="G40" s="23">
+        <v>18.1</v>
+      </c>
+      <c r="H40" s="23">
+        <v>62</v>
+      </c>
+      <c r="I40" s="23">
+        <v>0</v>
+      </c>
+      <c r="J40" s="22">
+        <v>0.25848</v>
+      </c>
+    </row>
+    <row r="41" ht="15" spans="1:10">
+      <c r="A41" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="22">
+        <v>81.98891</v>
+      </c>
+      <c r="D41" s="22">
+        <v>0.44233</v>
+      </c>
+      <c r="E41" s="23">
+        <v>0</v>
+      </c>
+      <c r="F41" s="22">
+        <v>17.32212</v>
+      </c>
+      <c r="G41" s="23">
+        <v>19.1</v>
+      </c>
+      <c r="H41" s="23">
+        <v>48.4</v>
+      </c>
+      <c r="I41" s="23">
+        <v>0</v>
+      </c>
+      <c r="J41" s="22">
+        <v>0.23989</v>
+      </c>
+    </row>
+    <row r="42" ht="15" spans="1:10">
+      <c r="A42" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="22">
+        <v>81.39819</v>
+      </c>
+      <c r="D42" s="22">
+        <v>0.44434</v>
+      </c>
+      <c r="E42" s="23">
+        <v>0</v>
+      </c>
+      <c r="F42" s="22">
+        <v>17.40719</v>
+      </c>
+      <c r="G42" s="23">
+        <v>15</v>
+      </c>
+      <c r="H42" s="23">
+        <v>49</v>
+      </c>
+      <c r="I42" s="23">
+        <v>0</v>
+      </c>
+      <c r="J42" s="22">
+        <v>0.74388</v>
+      </c>
+    </row>
+    <row r="43" ht="15" spans="1:10">
+      <c r="A43" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="22">
+        <v>81.55492</v>
+      </c>
+      <c r="D43" s="22">
+        <v>0.44413</v>
+      </c>
+      <c r="E43" s="23">
+        <v>0</v>
+      </c>
+      <c r="F43" s="22">
+        <v>17.47364</v>
+      </c>
+      <c r="G43" s="23">
+        <v>14.6</v>
+      </c>
+      <c r="H43" s="23">
+        <v>50.8</v>
+      </c>
+      <c r="I43" s="23">
+        <v>0</v>
+      </c>
+      <c r="J43" s="22">
+        <v>0.52077</v>
+      </c>
+    </row>
+    <row r="44" ht="15" spans="1:10">
+      <c r="A44" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="22">
+        <v>81.68259</v>
+      </c>
+      <c r="D44" s="22">
+        <v>0.44189</v>
+      </c>
+      <c r="E44" s="23">
+        <v>0</v>
+      </c>
+      <c r="F44" s="22">
+        <v>17.43107</v>
+      </c>
+      <c r="G44" s="23">
+        <v>18.2</v>
+      </c>
+      <c r="H44" s="23">
+        <v>49.8</v>
+      </c>
+      <c r="I44" s="23">
+        <v>0</v>
+      </c>
+      <c r="J44" s="22">
+        <v>0.43764</v>
+      </c>
+    </row>
+    <row r="45" ht="15" spans="1:10">
+      <c r="A45" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="22">
+        <v>81.86106</v>
+      </c>
+      <c r="D45" s="22">
+        <v>0.44188</v>
+      </c>
+      <c r="E45" s="23">
+        <v>0</v>
+      </c>
+      <c r="F45" s="22">
+        <v>17.38223</v>
+      </c>
+      <c r="G45" s="23">
+        <v>14.2</v>
+      </c>
+      <c r="H45" s="23">
+        <v>52.7</v>
+      </c>
+      <c r="I45" s="23">
+        <v>0</v>
+      </c>
+      <c r="J45" s="22">
+        <v>0.30814</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:10">
+      <c r="A46" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="22">
+        <v>79.61612</v>
+      </c>
+      <c r="D46" s="22">
+        <v>0.1359</v>
+      </c>
+      <c r="E46" s="23">
+        <v>0</v>
+      </c>
+      <c r="F46" s="22">
+        <v>20.24152</v>
+      </c>
+      <c r="G46" s="23">
+        <v>0</v>
+      </c>
+      <c r="H46" s="23">
+        <v>12</v>
+      </c>
+      <c r="I46" s="23">
+        <v>0</v>
+      </c>
+      <c r="J46" s="22">
+        <v>0.00526</v>
+      </c>
+    </row>
+    <row r="47" ht="15" spans="1:10">
+      <c r="A47" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="22">
+        <v>79.60239</v>
+      </c>
+      <c r="D47" s="22">
+        <v>0.14297</v>
+      </c>
+      <c r="E47" s="23">
+        <v>0</v>
+      </c>
+      <c r="F47" s="22">
+        <v>20.24461</v>
+      </c>
+      <c r="G47" s="23">
+        <v>0</v>
+      </c>
+      <c r="H47" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="I47" s="23">
+        <v>0</v>
+      </c>
+      <c r="J47" s="22">
+        <v>0.00947</v>
+      </c>
+    </row>
+    <row r="48" ht="15" spans="1:10">
+      <c r="A48" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="22">
+        <v>79.60741</v>
+      </c>
+      <c r="D48" s="22">
+        <v>0.13869</v>
+      </c>
+      <c r="E48" s="23">
+        <v>0</v>
+      </c>
+      <c r="F48" s="22">
+        <v>20.24417</v>
+      </c>
+      <c r="G48" s="23">
+        <v>0</v>
+      </c>
+      <c r="H48" s="23">
+        <v>13.2</v>
+      </c>
+      <c r="I48" s="23">
+        <v>0</v>
+      </c>
+      <c r="J48" s="22">
+        <v>0.00841</v>
+      </c>
+    </row>
+    <row r="49" ht="15" spans="1:10">
+      <c r="A49" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="22">
+        <v>79.60363</v>
+      </c>
+      <c r="D49" s="22">
+        <v>0.14241</v>
+      </c>
+      <c r="E49" s="23">
+        <v>0</v>
+      </c>
+      <c r="F49" s="22">
+        <v>20.24653</v>
+      </c>
+      <c r="G49" s="23">
+        <v>0</v>
+      </c>
+      <c r="H49" s="23">
+        <v>10.7</v>
+      </c>
+      <c r="I49" s="23">
+        <v>0</v>
+      </c>
+      <c r="J49" s="22">
+        <v>0.00637</v>
+      </c>
+    </row>
+    <row r="50" ht="15" spans="1:10">
+      <c r="A50" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="22">
+        <v>79.60885</v>
+      </c>
+      <c r="D50" s="22">
+        <v>0.14279</v>
+      </c>
+      <c r="E50" s="23">
+        <v>0</v>
+      </c>
+      <c r="F50" s="22">
+        <v>20.23795</v>
+      </c>
+      <c r="G50" s="23">
+        <v>0</v>
+      </c>
+      <c r="H50" s="23">
+        <v>16.6</v>
+      </c>
+      <c r="I50" s="23">
+        <v>0</v>
+      </c>
+      <c r="J50" s="22">
+        <v>0.00876</v>
+      </c>
+    </row>
+    <row r="51" ht="15" spans="1:10">
+      <c r="A51" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="22">
+        <v>79.60531</v>
+      </c>
+      <c r="D51" s="22">
+        <v>0.14508</v>
+      </c>
+      <c r="E51" s="23">
+        <v>0</v>
+      </c>
+      <c r="F51" s="22">
+        <v>20.23831</v>
+      </c>
+      <c r="G51" s="23">
+        <v>0</v>
+      </c>
+      <c r="H51" s="23">
+        <v>13.8</v>
+      </c>
+      <c r="I51" s="23">
+        <v>0</v>
+      </c>
+      <c r="J51" s="22">
+        <v>0.00992</v>
+      </c>
+    </row>
+    <row r="52" ht="15" spans="1:10">
+      <c r="A52" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="22">
+        <v>79.61531</v>
+      </c>
+      <c r="D52" s="22">
+        <v>0.1463</v>
+      </c>
+      <c r="E52" s="23">
+        <v>0</v>
+      </c>
+      <c r="F52" s="22">
+        <v>20.22792</v>
+      </c>
+      <c r="G52" s="23">
+        <v>0</v>
+      </c>
+      <c r="H52" s="23">
+        <v>5.6</v>
+      </c>
+      <c r="I52" s="23">
+        <v>0</v>
+      </c>
+      <c r="J52" s="22">
+        <v>0.00991</v>
+      </c>
+    </row>
+    <row r="53" ht="15" spans="1:10">
+      <c r="A53" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="22">
+        <v>79.61908</v>
+      </c>
+      <c r="D53" s="22">
+        <v>0.14954</v>
+      </c>
+      <c r="E53" s="23">
+        <v>0</v>
+      </c>
+      <c r="F53" s="22">
+        <v>20.21532</v>
+      </c>
+      <c r="G53" s="23">
+        <v>0</v>
+      </c>
+      <c r="H53" s="23">
+        <v>12.6</v>
+      </c>
+      <c r="I53" s="23">
+        <v>0</v>
+      </c>
+      <c r="J53" s="22">
+        <v>0.0148</v>
+      </c>
+    </row>
+    <row r="54" ht="15" spans="1:10">
+      <c r="A54" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="22">
+        <v>79.61739</v>
+      </c>
+      <c r="D54" s="22">
+        <v>0.15143</v>
+      </c>
+      <c r="E54" s="23">
+        <v>0</v>
+      </c>
+      <c r="F54" s="22">
+        <v>20.21877</v>
+      </c>
+      <c r="G54" s="23">
+        <v>0</v>
+      </c>
+      <c r="H54" s="23">
+        <v>16.6</v>
+      </c>
+      <c r="I54" s="23">
+        <v>0</v>
+      </c>
+      <c r="J54" s="22">
+        <v>0.01074</v>
+      </c>
+    </row>
+    <row r="55" ht="15" spans="1:10">
+      <c r="A55" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="22">
+        <v>79.63747</v>
+      </c>
+      <c r="D55" s="22">
+        <v>0.14502</v>
+      </c>
+      <c r="E55" s="23">
+        <v>0</v>
+      </c>
+      <c r="F55" s="22">
+        <v>20.19955</v>
+      </c>
+      <c r="G55" s="23">
+        <v>0</v>
+      </c>
+      <c r="H55" s="23">
+        <v>21.4</v>
+      </c>
+      <c r="I55" s="23">
+        <v>0</v>
+      </c>
+      <c r="J55" s="22">
+        <v>0.01581</v>
+      </c>
+    </row>
+    <row r="56" ht="15" spans="1:10">
+      <c r="A56" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="22">
+        <v>79.65502</v>
+      </c>
+      <c r="D56" s="22">
+        <v>0.14949</v>
+      </c>
+      <c r="E56" s="23">
+        <v>0</v>
+      </c>
+      <c r="F56" s="22">
+        <v>20.17608</v>
+      </c>
+      <c r="G56" s="23">
+        <v>0</v>
+      </c>
+      <c r="H56" s="23">
+        <v>14.1</v>
+      </c>
+      <c r="I56" s="23">
+        <v>0</v>
+      </c>
+      <c r="J56" s="22">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="57" ht="15" spans="1:10">
+      <c r="A57" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="22">
+        <v>79.64436</v>
+      </c>
+      <c r="D57" s="22">
+        <v>0.14558</v>
+      </c>
+      <c r="E57" s="23">
+        <v>0</v>
+      </c>
+      <c r="F57" s="22">
+        <v>20.19073</v>
+      </c>
+      <c r="G57" s="23">
+        <v>0</v>
+      </c>
+      <c r="H57" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="I57" s="23">
+        <v>0</v>
+      </c>
+      <c r="J57" s="22">
+        <v>0.01932</v>
+      </c>
+    </row>
+    <row r="58" ht="15" spans="1:10">
+      <c r="A58" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" s="22">
+        <v>79.65282</v>
+      </c>
+      <c r="D58" s="22">
+        <v>0.12027</v>
+      </c>
+      <c r="E58" s="23">
+        <v>0</v>
+      </c>
+      <c r="F58" s="22">
+        <v>20.20247</v>
+      </c>
+      <c r="G58" s="23">
+        <v>0</v>
+      </c>
+      <c r="H58" s="23">
+        <v>18.9</v>
+      </c>
+      <c r="I58" s="23">
+        <v>0</v>
+      </c>
+      <c r="J58" s="22">
+        <v>0.02255</v>
+      </c>
+    </row>
+    <row r="59" ht="15" spans="1:10">
+      <c r="A59" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="22">
+        <v>79.6329</v>
+      </c>
+      <c r="D59" s="22">
+        <v>0.1557</v>
+      </c>
+      <c r="E59" s="23">
+        <v>0</v>
+      </c>
+      <c r="F59" s="22">
+        <v>20.18617</v>
+      </c>
+      <c r="G59" s="23">
+        <v>0</v>
+      </c>
+      <c r="H59" s="23">
+        <v>7.8</v>
+      </c>
+      <c r="I59" s="23">
+        <v>0</v>
+      </c>
+      <c r="J59" s="22">
+        <v>0.02446</v>
+      </c>
+    </row>
+    <row r="60" ht="15" spans="1:10">
+      <c r="A60" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="22">
+        <v>79.65955</v>
+      </c>
+      <c r="D60" s="22">
+        <v>0.15199</v>
+      </c>
+      <c r="E60" s="23">
+        <v>0</v>
+      </c>
+      <c r="F60" s="22">
+        <v>20.16149</v>
+      </c>
+      <c r="G60" s="23">
+        <v>0</v>
+      </c>
+      <c r="H60" s="23">
+        <v>5.1</v>
+      </c>
+      <c r="I60" s="23">
+        <v>0</v>
+      </c>
+      <c r="J60" s="22">
+        <v>0.02646</v>
+      </c>
+    </row>
+    <row r="61" ht="15" spans="1:10">
+      <c r="A61" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="22">
+        <v>79.61407</v>
+      </c>
+      <c r="D61" s="22">
+        <v>0.15021</v>
+      </c>
+      <c r="E61" s="23">
+        <v>0</v>
+      </c>
+      <c r="F61" s="22">
+        <v>20.1977</v>
+      </c>
+      <c r="G61" s="23">
+        <v>0</v>
+      </c>
+      <c r="H61" s="23">
+        <v>0</v>
+      </c>
+      <c r="I61" s="23">
+        <v>0</v>
+      </c>
+      <c r="J61" s="22">
+        <v>0.03803</v>
+      </c>
+    </row>
+    <row r="62" ht="15" spans="1:10">
+      <c r="A62" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="22">
+        <v>79.62184</v>
+      </c>
+      <c r="D62" s="22">
+        <v>0.14727</v>
+      </c>
+      <c r="E62" s="23">
+        <v>0</v>
+      </c>
+      <c r="F62" s="22">
+        <v>20.19237</v>
+      </c>
+      <c r="G62" s="23">
+        <v>0</v>
+      </c>
+      <c r="H62" s="23">
+        <v>12</v>
+      </c>
+      <c r="I62" s="23">
+        <v>0</v>
+      </c>
+      <c r="J62" s="22">
+        <v>0.03733</v>
+      </c>
+    </row>
+    <row r="63" ht="15" spans="1:10">
+      <c r="A63" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C63" s="22">
+        <v>79.62681</v>
+      </c>
+      <c r="D63" s="22">
+        <v>0.1443</v>
+      </c>
+      <c r="E63" s="23">
+        <v>0</v>
+      </c>
+      <c r="F63" s="22">
+        <v>20.18239</v>
+      </c>
+      <c r="G63" s="23">
+        <v>0</v>
+      </c>
+      <c r="H63" s="23">
+        <v>15.2</v>
+      </c>
+      <c r="I63" s="23">
+        <v>0</v>
+      </c>
+      <c r="J63" s="22">
+        <v>0.04498</v>
+      </c>
+    </row>
+    <row r="64" ht="15" spans="1:10">
+      <c r="A64" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="22">
+        <v>79.57635</v>
+      </c>
+      <c r="D64" s="22">
+        <v>0.14385</v>
+      </c>
+      <c r="E64" s="23">
+        <v>0</v>
+      </c>
+      <c r="F64" s="22">
+        <v>20.19322</v>
+      </c>
+      <c r="G64" s="23">
+        <v>0</v>
+      </c>
+      <c r="H64" s="23">
+        <v>0</v>
+      </c>
+      <c r="I64" s="23">
+        <v>0</v>
+      </c>
+      <c r="J64" s="22">
+        <v>0.08657</v>
+      </c>
+    </row>
+    <row r="65" ht="15" spans="1:10">
+      <c r="A65" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" s="22">
+        <v>79.57614</v>
+      </c>
+      <c r="D65" s="22">
+        <v>0.14019</v>
+      </c>
+      <c r="E65" s="23">
+        <v>0</v>
+      </c>
+      <c r="F65" s="22">
+        <v>20.20497</v>
+      </c>
+      <c r="G65" s="23">
+        <v>0</v>
+      </c>
+      <c r="H65" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="I65" s="23">
+        <v>0</v>
+      </c>
+      <c r="J65" s="22">
+        <v>0.07862</v>
+      </c>
+    </row>
+    <row r="66" ht="15" spans="1:10">
+      <c r="A66" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="22">
+        <v>79.59612</v>
+      </c>
+      <c r="D66" s="22">
+        <v>0.14104</v>
+      </c>
+      <c r="E66" s="23">
+        <v>0</v>
+      </c>
+      <c r="F66" s="22">
+        <v>20.19971</v>
+      </c>
+      <c r="G66" s="23">
+        <v>0</v>
+      </c>
+      <c r="H66" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="I66" s="23">
+        <v>0</v>
+      </c>
+      <c r="J66" s="22">
+        <v>0.06298</v>
+      </c>
+    </row>
+    <row r="67" ht="15" spans="1:10">
+      <c r="A67" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C67" s="22">
+        <v>79.58314</v>
+      </c>
+      <c r="D67" s="22">
+        <v>0.14392</v>
+      </c>
+      <c r="E67" s="23">
+        <v>0</v>
+      </c>
+      <c r="F67" s="22">
+        <v>20.21043</v>
+      </c>
+      <c r="G67" s="23">
+        <v>0</v>
+      </c>
+      <c r="H67" s="23">
+        <v>3.5</v>
+      </c>
+      <c r="I67" s="23">
+        <v>0</v>
+      </c>
+      <c r="J67" s="22">
+        <v>0.06218</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:C23">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:C45">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C46:C67">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -1884,7 +4310,7 @@
     </row>
     <row r="17" ht="15" spans="1:10">
       <c r="A17" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B17" s="4">
         <v>46270.0221180556</v>
@@ -1916,7 +4342,7 @@
     </row>
     <row r="18" ht="15" spans="1:10">
       <c r="A18" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B18" s="4">
         <v>46270.0556365741</v>
@@ -1948,7 +4374,7 @@
     </row>
     <row r="19" ht="15" spans="1:10">
       <c r="A19" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B19" s="4">
         <v>46270.0891435185</v>
@@ -1980,7 +4406,7 @@
     </row>
     <row r="20" ht="15" spans="1:10">
       <c r="A20" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B20" s="4">
         <v>46270.1729050926</v>
@@ -2012,7 +4438,7 @@
     </row>
     <row r="21" ht="15" spans="1:10">
       <c r="A21" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B21" s="4">
         <v>46270.2231597222</v>
@@ -2044,7 +4470,7 @@
     </row>
     <row r="22" ht="15" spans="1:10">
       <c r="A22" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B22" s="4">
         <v>46270.2566666667</v>
@@ -2076,7 +4502,7 @@
     </row>
     <row r="23" ht="15" spans="1:10">
       <c r="A23" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B23" s="4">
         <v>46270.3069328704</v>
@@ -2108,7 +4534,7 @@
     </row>
     <row r="24" ht="15" spans="1:10">
       <c r="A24" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B24" s="4">
         <v>46270.0165393519</v>
@@ -2140,7 +4566,7 @@
     </row>
     <row r="25" ht="15" spans="1:10">
       <c r="A25" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B25" s="4">
         <v>46270.0500578704</v>
@@ -2172,7 +4598,7 @@
     </row>
     <row r="26" ht="15" spans="1:10">
       <c r="A26" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B26" s="4">
         <v>46270.0835648148</v>
@@ -2204,7 +4630,7 @@
     </row>
     <row r="27" ht="15" spans="1:10">
       <c r="A27" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4">
         <v>46270.1673263889</v>
@@ -2236,7 +4662,7 @@
     </row>
     <row r="28" ht="15" spans="1:10">
       <c r="A28" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B28" s="4">
         <v>46270.2175810185</v>
@@ -2268,7 +4694,7 @@
     </row>
     <row r="29" ht="15" spans="1:10">
       <c r="A29" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B29" s="4">
         <v>46270.251087963</v>
@@ -2300,7 +4726,7 @@
     </row>
     <row r="30" ht="15" spans="1:10">
       <c r="A30" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B30" s="4">
         <v>46270.3013541667</v>
@@ -2332,7 +4758,7 @@
     </row>
     <row r="31" ht="15" spans="1:10">
       <c r="A31" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B31" s="4">
         <v>46269.0443981482</v>
@@ -2364,7 +4790,7 @@
     </row>
     <row r="32" ht="15" spans="1:10">
       <c r="A32" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B32" s="4">
         <v>46269.0890740741</v>
@@ -2396,13 +4822,13 @@
     </row>
     <row r="33" ht="15" spans="1:10">
       <c r="A33" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B33" s="4">
         <v>46269.1337615741</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="D33" s="6">
         <v>0.44416</v>
@@ -2428,7 +4854,7 @@
     </row>
     <row r="34" ht="15" spans="1:10">
       <c r="A34" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B34" s="4">
         <v>46269.1672800926</v>
@@ -2460,7 +4886,7 @@
     </row>
     <row r="35" ht="15" spans="1:10">
       <c r="A35" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B35" s="4">
         <v>46269.2119560185</v>
@@ -2492,7 +4918,7 @@
     </row>
     <row r="36" ht="15" spans="1:10">
       <c r="A36" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B36" s="4">
         <v>46269.2454861111</v>
@@ -2524,10 +4950,10 @@
     </row>
     <row r="37" ht="15" spans="1:10">
       <c r="A37" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="C37" s="6">
         <v>81.22459</v>
@@ -2556,7 +4982,7 @@
     </row>
     <row r="38" ht="15" spans="1:10">
       <c r="A38" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B38" s="4">
         <v>46269.3460416667</v>

--- a/cfdata.xlsx
+++ b/cfdata.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
   <si>
     <t>采样地点</t>
   </si>
@@ -267,11 +267,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -882,7 +883,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -891,6 +892,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -944,7 +948,17 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1138,25 +1152,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2516,8 +2530,8 @@
       <c r="A32" t="s">
         <v>33</v>
       </c>
-      <c r="B32" t="s">
-        <v>19</v>
+      <c r="B32" s="3">
+        <v>46271.1511458333</v>
       </c>
       <c r="C32">
         <v>9</v>
@@ -3773,6 +3787,9 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B67">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/cfdata.xlsx
+++ b/cfdata.xlsx
@@ -32,10 +32,10 @@
     <t>采样地点</t>
   </si>
   <si>
+    <t>循环次数</t>
+  </si>
+  <si>
     <t>采样日期时间</t>
-  </si>
-  <si>
-    <t>循环次数</t>
   </si>
   <si>
     <t>N2</t>
@@ -1435,8 +1435,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.575" customWidth="1"/>
-    <col min="2" max="2" width="24.125" customWidth="1"/>
-    <col min="3" max="3" width="14.125" customWidth="1"/>
+    <col min="2" max="2" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="24.125" customWidth="1"/>
     <col min="4" max="4" width="11.625" customWidth="1"/>
     <col min="5" max="5" width="10.375" customWidth="1"/>
     <col min="7" max="7" width="11.625" customWidth="1"/>
@@ -1480,11 +1480,11 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
       </c>
       <c r="D2">
         <v>80.79627</v>
@@ -1515,11 +1515,11 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
       </c>
       <c r="D3">
         <v>80.85424</v>
@@ -1550,11 +1550,11 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
       </c>
       <c r="D4">
         <v>80.8857</v>
@@ -1585,11 +1585,11 @@
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
       </c>
       <c r="D5">
         <v>80.88314</v>
@@ -1620,11 +1620,11 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
       </c>
       <c r="D6">
         <v>80.85319</v>
@@ -1655,11 +1655,11 @@
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>16</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
       <c r="D7">
         <v>80.8053</v>
@@ -1690,11 +1690,11 @@
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
       </c>
       <c r="D8">
         <v>80.79943</v>
@@ -1725,11 +1725,11 @@
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>18</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
       </c>
       <c r="D9">
         <v>80.96898</v>
@@ -1760,11 +1760,11 @@
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
       </c>
       <c r="D10">
         <v>80.9102</v>
@@ -1795,11 +1795,11 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
       </c>
       <c r="D11">
         <v>80.90591</v>
@@ -1830,11 +1830,11 @@
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
         <v>21</v>
-      </c>
-      <c r="C12">
-        <v>11</v>
       </c>
       <c r="D12">
         <v>80.91769</v>
@@ -1865,11 +1865,11 @@
       <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
         <v>22</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
       </c>
       <c r="D13">
         <v>80.91144</v>
@@ -1900,11 +1900,11 @@
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
         <v>23</v>
-      </c>
-      <c r="C14">
-        <v>13</v>
       </c>
       <c r="D14">
         <v>80.86653</v>
@@ -1935,11 +1935,11 @@
       <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
         <v>24</v>
-      </c>
-      <c r="C15">
-        <v>14</v>
       </c>
       <c r="D15">
         <v>80.86792</v>
@@ -1970,11 +1970,11 @@
       <c r="A16" t="s">
         <v>10</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
         <v>25</v>
-      </c>
-      <c r="C16">
-        <v>15</v>
       </c>
       <c r="D16">
         <v>80.85043</v>
@@ -2005,11 +2005,11 @@
       <c r="A17" t="s">
         <v>10</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
         <v>26</v>
-      </c>
-      <c r="C17">
-        <v>16</v>
       </c>
       <c r="D17">
         <v>80.77438</v>
@@ -2040,11 +2040,11 @@
       <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
         <v>27</v>
-      </c>
-      <c r="C18">
-        <v>17</v>
       </c>
       <c r="D18">
         <v>80.77319</v>
@@ -2075,11 +2075,11 @@
       <c r="A19" t="s">
         <v>10</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
         <v>28</v>
-      </c>
-      <c r="C19">
-        <v>18</v>
       </c>
       <c r="D19">
         <v>80.7879</v>
@@ -2110,11 +2110,11 @@
       <c r="A20" t="s">
         <v>10</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
         <v>29</v>
-      </c>
-      <c r="C20">
-        <v>19</v>
       </c>
       <c r="D20">
         <v>80.46644</v>
@@ -2145,11 +2145,11 @@
       <c r="A21" t="s">
         <v>10</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
         <v>30</v>
-      </c>
-      <c r="C21">
-        <v>20</v>
       </c>
       <c r="D21">
         <v>80.52477</v>
@@ -2180,11 +2180,11 @@
       <c r="A22" t="s">
         <v>10</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
         <v>31</v>
-      </c>
-      <c r="C22">
-        <v>21</v>
       </c>
       <c r="D22">
         <v>80.63069</v>
@@ -2215,11 +2215,11 @@
       <c r="A23" t="s">
         <v>10</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
         <v>32</v>
-      </c>
-      <c r="C23">
-        <v>22</v>
       </c>
       <c r="D23">
         <v>80.61491</v>
@@ -2250,11 +2250,11 @@
       <c r="A24" t="s">
         <v>33</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
         <v>34</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
       </c>
       <c r="D24">
         <v>81.99542</v>
@@ -2285,11 +2285,11 @@
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
         <v>35</v>
-      </c>
-      <c r="C25">
-        <v>2</v>
       </c>
       <c r="D25">
         <v>82.08538</v>
@@ -2320,11 +2320,11 @@
       <c r="A26" t="s">
         <v>33</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
         <v>36</v>
-      </c>
-      <c r="C26">
-        <v>3</v>
       </c>
       <c r="D26">
         <v>82.05372</v>
@@ -2355,11 +2355,11 @@
       <c r="A27" t="s">
         <v>33</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
         <v>37</v>
-      </c>
-      <c r="C27">
-        <v>4</v>
       </c>
       <c r="D27">
         <v>82.08195</v>
@@ -2390,11 +2390,11 @@
       <c r="A28" t="s">
         <v>33</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
         <v>38</v>
-      </c>
-      <c r="C28">
-        <v>5</v>
       </c>
       <c r="D28">
         <v>82.05914</v>
@@ -2425,11 +2425,11 @@
       <c r="A29" t="s">
         <v>33</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
         <v>39</v>
-      </c>
-      <c r="C29">
-        <v>6</v>
       </c>
       <c r="D29">
         <v>82.03971</v>
@@ -2460,11 +2460,11 @@
       <c r="A30" t="s">
         <v>33</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
         <v>40</v>
-      </c>
-      <c r="C30">
-        <v>7</v>
       </c>
       <c r="D30">
         <v>82.02074</v>
@@ -2495,11 +2495,11 @@
       <c r="A31" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
         <v>41</v>
-      </c>
-      <c r="C31">
-        <v>8</v>
       </c>
       <c r="D31">
         <v>82.00478</v>
@@ -2530,11 +2530,11 @@
       <c r="A32" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3">
         <v>46271.1511458333</v>
-      </c>
-      <c r="C32">
-        <v>9</v>
       </c>
       <c r="D32">
         <v>81.98119</v>
@@ -2565,11 +2565,11 @@
       <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
         <v>42</v>
-      </c>
-      <c r="C33">
-        <v>10</v>
       </c>
       <c r="D33">
         <v>82.05141</v>
@@ -2600,11 +2600,11 @@
       <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
         <v>43</v>
-      </c>
-      <c r="C34">
-        <v>11</v>
       </c>
       <c r="D34">
         <v>82.10519</v>
@@ -2635,11 +2635,11 @@
       <c r="A35" t="s">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
         <v>44</v>
-      </c>
-      <c r="C35">
-        <v>12</v>
       </c>
       <c r="D35">
         <v>82.03838</v>
@@ -2670,11 +2670,11 @@
       <c r="A36" t="s">
         <v>33</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36">
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
         <v>45</v>
-      </c>
-      <c r="C36">
-        <v>13</v>
       </c>
       <c r="D36">
         <v>81.9981</v>
@@ -2705,11 +2705,11 @@
       <c r="A37" t="s">
         <v>33</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
         <v>46</v>
-      </c>
-      <c r="C37">
-        <v>14</v>
       </c>
       <c r="D37">
         <v>81.99336</v>
@@ -2740,11 +2740,11 @@
       <c r="A38" t="s">
         <v>33</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38">
+        <v>15</v>
+      </c>
+      <c r="C38" t="s">
         <v>47</v>
-      </c>
-      <c r="C38">
-        <v>15</v>
       </c>
       <c r="D38">
         <v>81.99844</v>
@@ -2775,11 +2775,11 @@
       <c r="A39" t="s">
         <v>33</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39">
+        <v>16</v>
+      </c>
+      <c r="C39" t="s">
         <v>48</v>
-      </c>
-      <c r="C39">
-        <v>16</v>
       </c>
       <c r="D39">
         <v>81.96129</v>
@@ -2810,11 +2810,11 @@
       <c r="A40" t="s">
         <v>33</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40">
+        <v>17</v>
+      </c>
+      <c r="C40" t="s">
         <v>49</v>
-      </c>
-      <c r="C40">
-        <v>17</v>
       </c>
       <c r="D40">
         <v>81.98632</v>
@@ -2845,11 +2845,11 @@
       <c r="A41" t="s">
         <v>33</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
         <v>50</v>
-      </c>
-      <c r="C41">
-        <v>18</v>
       </c>
       <c r="D41">
         <v>81.98891</v>
@@ -2880,11 +2880,11 @@
       <c r="A42" t="s">
         <v>33</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
         <v>51</v>
-      </c>
-      <c r="C42">
-        <v>19</v>
       </c>
       <c r="D42">
         <v>81.39819</v>
@@ -2915,11 +2915,11 @@
       <c r="A43" t="s">
         <v>33</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43">
+        <v>20</v>
+      </c>
+      <c r="C43" t="s">
         <v>52</v>
-      </c>
-      <c r="C43">
-        <v>20</v>
       </c>
       <c r="D43">
         <v>81.55492</v>
@@ -2950,11 +2950,11 @@
       <c r="A44" t="s">
         <v>33</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44">
+        <v>21</v>
+      </c>
+      <c r="C44" t="s">
         <v>53</v>
-      </c>
-      <c r="C44">
-        <v>21</v>
       </c>
       <c r="D44">
         <v>81.68259</v>
@@ -2985,11 +2985,11 @@
       <c r="A45" t="s">
         <v>33</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
         <v>54</v>
-      </c>
-      <c r="C45">
-        <v>22</v>
       </c>
       <c r="D45">
         <v>81.86106</v>
@@ -3020,11 +3020,11 @@
       <c r="A46" t="s">
         <v>55</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
         <v>56</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
       </c>
       <c r="D46">
         <v>79.61612</v>
@@ -3055,11 +3055,11 @@
       <c r="A47" t="s">
         <v>55</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
         <v>57</v>
-      </c>
-      <c r="C47">
-        <v>2</v>
       </c>
       <c r="D47">
         <v>79.60239</v>
@@ -3090,11 +3090,11 @@
       <c r="A48" t="s">
         <v>55</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s">
         <v>58</v>
-      </c>
-      <c r="C48">
-        <v>3</v>
       </c>
       <c r="D48">
         <v>79.60741</v>
@@ -3125,11 +3125,11 @@
       <c r="A49" t="s">
         <v>55</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
         <v>59</v>
-      </c>
-      <c r="C49">
-        <v>4</v>
       </c>
       <c r="D49">
         <v>79.60363</v>
@@ -3160,11 +3160,11 @@
       <c r="A50" t="s">
         <v>55</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
         <v>60</v>
-      </c>
-      <c r="C50">
-        <v>5</v>
       </c>
       <c r="D50">
         <v>79.60885</v>
@@ -3195,11 +3195,11 @@
       <c r="A51" t="s">
         <v>55</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
         <v>61</v>
-      </c>
-      <c r="C51">
-        <v>6</v>
       </c>
       <c r="D51">
         <v>79.60531</v>
@@ -3230,11 +3230,11 @@
       <c r="A52" t="s">
         <v>55</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
         <v>62</v>
-      </c>
-      <c r="C52">
-        <v>7</v>
       </c>
       <c r="D52">
         <v>79.61531</v>
@@ -3265,11 +3265,11 @@
       <c r="A53" t="s">
         <v>55</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
         <v>63</v>
-      </c>
-      <c r="C53">
-        <v>8</v>
       </c>
       <c r="D53">
         <v>79.61908</v>
@@ -3300,11 +3300,11 @@
       <c r="A54" t="s">
         <v>55</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
         <v>64</v>
-      </c>
-      <c r="C54">
-        <v>9</v>
       </c>
       <c r="D54">
         <v>79.61739</v>
@@ -3335,11 +3335,11 @@
       <c r="A55" t="s">
         <v>55</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s">
         <v>65</v>
-      </c>
-      <c r="C55">
-        <v>10</v>
       </c>
       <c r="D55">
         <v>79.63747</v>
@@ -3370,11 +3370,11 @@
       <c r="A56" t="s">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
         <v>66</v>
-      </c>
-      <c r="C56">
-        <v>11</v>
       </c>
       <c r="D56">
         <v>79.65502</v>
@@ -3405,11 +3405,11 @@
       <c r="A57" t="s">
         <v>55</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57">
+        <v>12</v>
+      </c>
+      <c r="C57" t="s">
         <v>67</v>
-      </c>
-      <c r="C57">
-        <v>12</v>
       </c>
       <c r="D57">
         <v>79.64436</v>
@@ -3440,11 +3440,11 @@
       <c r="A58" t="s">
         <v>55</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58">
+        <v>13</v>
+      </c>
+      <c r="C58" t="s">
         <v>68</v>
-      </c>
-      <c r="C58">
-        <v>13</v>
       </c>
       <c r="D58">
         <v>79.65282</v>
@@ -3475,11 +3475,11 @@
       <c r="A59" t="s">
         <v>55</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59">
+        <v>14</v>
+      </c>
+      <c r="C59" t="s">
         <v>69</v>
-      </c>
-      <c r="C59">
-        <v>14</v>
       </c>
       <c r="D59">
         <v>79.6329</v>
@@ -3510,11 +3510,11 @@
       <c r="A60" t="s">
         <v>55</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60">
+        <v>15</v>
+      </c>
+      <c r="C60" t="s">
         <v>70</v>
-      </c>
-      <c r="C60">
-        <v>15</v>
       </c>
       <c r="D60">
         <v>79.65955</v>
@@ -3545,11 +3545,11 @@
       <c r="A61" t="s">
         <v>55</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61">
+        <v>16</v>
+      </c>
+      <c r="C61" t="s">
         <v>71</v>
-      </c>
-      <c r="C61">
-        <v>16</v>
       </c>
       <c r="D61">
         <v>79.61407</v>
@@ -3580,11 +3580,11 @@
       <c r="A62" t="s">
         <v>55</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62">
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
         <v>72</v>
-      </c>
-      <c r="C62">
-        <v>17</v>
       </c>
       <c r="D62">
         <v>79.62184</v>
@@ -3615,11 +3615,11 @@
       <c r="A63" t="s">
         <v>55</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
         <v>73</v>
-      </c>
-      <c r="C63">
-        <v>18</v>
       </c>
       <c r="D63">
         <v>79.62681</v>
@@ -3650,11 +3650,11 @@
       <c r="A64" t="s">
         <v>55</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64">
+        <v>19</v>
+      </c>
+      <c r="C64" t="s">
         <v>74</v>
-      </c>
-      <c r="C64">
-        <v>19</v>
       </c>
       <c r="D64">
         <v>79.57635</v>
@@ -3685,11 +3685,11 @@
       <c r="A65" t="s">
         <v>55</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65">
+        <v>20</v>
+      </c>
+      <c r="C65" t="s">
         <v>75</v>
-      </c>
-      <c r="C65">
-        <v>20</v>
       </c>
       <c r="D65">
         <v>79.57614</v>
@@ -3720,11 +3720,11 @@
       <c r="A66" t="s">
         <v>55</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66">
+        <v>21</v>
+      </c>
+      <c r="C66" t="s">
         <v>76</v>
-      </c>
-      <c r="C66">
-        <v>21</v>
       </c>
       <c r="D66">
         <v>79.59612</v>
@@ -3755,11 +3755,11 @@
       <c r="A67" t="s">
         <v>55</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67">
+        <v>22</v>
+      </c>
+      <c r="C67" t="s">
         <v>77</v>
-      </c>
-      <c r="C67">
-        <v>22</v>
       </c>
       <c r="D67">
         <v>79.58314</v>
@@ -3787,7 +3787,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B67">
+  <conditionalFormatting sqref="C2:C67">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cfdata.xlsx
+++ b/cfdata.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView windowWidth="27930" windowHeight="12975" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="12802采空区" sheetId="1" r:id="rId1"/>
+    <sheet name="12803采空区（回风巷）" sheetId="2" r:id="rId2"/>
+    <sheet name="12803采空区（运输巷）" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="78">
   <si>
     <t>采样地点</t>
   </si>
@@ -883,7 +885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -892,6 +894,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1431,7 +1436,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.575" customWidth="1"/>
@@ -2248,37 +2253,1529 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3">
+        <v>46272.0091087963</v>
+      </c>
+      <c r="D24">
+        <v>80.68496</v>
+      </c>
+      <c r="E24">
+        <v>0.45296</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>18.47761</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0.38447</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3">
+        <v>46272.0258680556</v>
+      </c>
+      <c r="D25">
+        <v>80.87077</v>
+      </c>
+      <c r="E25">
+        <v>0.4457</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>18.3033</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0.38004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3">
+        <v>46272.0426157407</v>
+      </c>
+      <c r="D26">
+        <v>80.87899</v>
+      </c>
+      <c r="E26">
+        <v>0.44472</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>18.2969</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>1.2</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0.37926</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3">
+        <v>46272.0593634259</v>
+      </c>
+      <c r="D27">
+        <v>80.81437</v>
+      </c>
+      <c r="E27">
+        <v>0.44672</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>18.35418</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>2.1</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0.38453</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3">
+        <v>46272.076099537</v>
+      </c>
+      <c r="D28">
+        <v>80.81229</v>
+      </c>
+      <c r="E28">
+        <v>0.44909</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>18.35477</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0.38384</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29" s="3">
+        <v>46272.0928587963</v>
+      </c>
+      <c r="D29">
+        <v>80.83635</v>
+      </c>
+      <c r="E29">
+        <v>0.44723</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>18.32948</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>6.7</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0.38627</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30" s="3">
+        <v>46272.1095949074</v>
+      </c>
+      <c r="D30">
+        <v>80.81064</v>
+      </c>
+      <c r="E30">
+        <v>0.44906</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>18.35622</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>3.6</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0.38371</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31" s="3">
+        <v>46272.1263425926</v>
+      </c>
+      <c r="D31">
+        <v>80.82309</v>
+      </c>
+      <c r="E31">
+        <v>0.44886</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>18.35435</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0.37369</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3">
+        <v>46272.1430902778</v>
+      </c>
+      <c r="D32">
+        <v>80.81859</v>
+      </c>
+      <c r="E32">
+        <v>0.44808</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>18.35562</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0.37772</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3">
+        <v>46272.159837963</v>
+      </c>
+      <c r="D33">
+        <v>80.80074</v>
+      </c>
+      <c r="E33">
+        <v>0.44939</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>18.37494</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>4.1</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0.37452</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34">
+        <v>11</v>
+      </c>
+      <c r="C34" s="3">
+        <v>46272.1765856482</v>
+      </c>
+      <c r="D34">
+        <v>80.7879</v>
+      </c>
+      <c r="E34">
+        <v>0.44962</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>18.39182</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0.37065</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35">
+        <v>12</v>
+      </c>
+      <c r="C35" s="3">
+        <v>46272.1933217593</v>
+      </c>
+      <c r="D35">
+        <v>80.811</v>
+      </c>
+      <c r="E35">
+        <v>0.44811</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>18.37314</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0.36775</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36">
+        <v>13</v>
+      </c>
+      <c r="C36" s="3">
+        <v>46272.2100694444</v>
+      </c>
+      <c r="D36">
+        <v>80.8467</v>
+      </c>
+      <c r="E36">
+        <v>0.44804</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>18.34914</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0.35611</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37">
+        <v>14</v>
+      </c>
+      <c r="C37" s="3">
+        <v>46272.2268055556</v>
+      </c>
+      <c r="D37">
+        <v>80.87362</v>
+      </c>
+      <c r="E37">
+        <v>0.44766</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>18.32519</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0.35353</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38">
+        <v>15</v>
+      </c>
+      <c r="C38" s="3">
+        <v>46272.2435416667</v>
+      </c>
+      <c r="D38">
+        <v>80.79147</v>
+      </c>
+      <c r="E38">
+        <v>0.44975</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>18.41549</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>3.9</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0.3429</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39">
+        <v>16</v>
+      </c>
+      <c r="C39" s="3">
+        <v>46272.2602777778</v>
+      </c>
+      <c r="D39">
+        <v>80.81857</v>
+      </c>
+      <c r="E39">
+        <v>0.44881</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>18.39931</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>6.7</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0.33263</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40">
+        <v>17</v>
+      </c>
+      <c r="C40" s="3">
+        <v>46272.277037037</v>
+      </c>
+      <c r="D40">
+        <v>80.83416</v>
+      </c>
+      <c r="E40">
+        <v>0.44806</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>18.39732</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0.32007</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41">
+        <v>18</v>
+      </c>
+      <c r="C41" s="3">
+        <v>46272.2937962963</v>
+      </c>
+      <c r="D41">
+        <v>80.89694</v>
+      </c>
+      <c r="E41">
+        <v>0.44593</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>18.35378</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>4.2</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0.30292</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42">
+        <v>19</v>
+      </c>
+      <c r="C42" s="3">
+        <v>46272.3105555556</v>
+      </c>
+      <c r="D42">
+        <v>80.87537</v>
+      </c>
+      <c r="E42">
+        <v>0.44597</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>18.38783</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0.29084</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:C23">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="23.575" customWidth="1"/>
+    <col min="2" max="2" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="24.125" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="10.375" customWidth="1"/>
+    <col min="7" max="7" width="11.625" customWidth="1"/>
+    <col min="11" max="11" width="11.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
       </c>
+      <c r="D2">
+        <v>81.99542</v>
+      </c>
+      <c r="E2">
+        <v>0.39205</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>17.56161</v>
+      </c>
+      <c r="H2">
+        <v>17.9</v>
+      </c>
+      <c r="I2">
+        <v>48</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.04434</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3">
+        <v>82.08538</v>
+      </c>
+      <c r="E3">
+        <v>0.3996</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>17.46044</v>
+      </c>
+      <c r="H3">
+        <v>18.1</v>
+      </c>
+      <c r="I3">
+        <v>62.9</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.04647</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4">
+        <v>82.05372</v>
+      </c>
+      <c r="E4">
+        <v>0.41003</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>17.448</v>
+      </c>
+      <c r="H4">
+        <v>16.7</v>
+      </c>
+      <c r="I4">
+        <v>61</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.07048</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <v>82.08195</v>
+      </c>
+      <c r="E5">
+        <v>0.40991</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>17.45259</v>
+      </c>
+      <c r="H5">
+        <v>17.4</v>
+      </c>
+      <c r="I5">
+        <v>63.4</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.04748</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6">
+        <v>82.05914</v>
+      </c>
+      <c r="E6">
+        <v>0.41312</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>17.45248</v>
+      </c>
+      <c r="H6">
+        <v>17.9</v>
+      </c>
+      <c r="I6">
+        <v>60.1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0.06747</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>82.03971</v>
+      </c>
+      <c r="E7">
+        <v>0.41467</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>17.47815</v>
+      </c>
+      <c r="H7">
+        <v>17.9</v>
+      </c>
+      <c r="I7">
+        <v>61.1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.05958</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8">
+        <v>82.02074</v>
+      </c>
+      <c r="E8">
+        <v>0.4145</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>17.48058</v>
+      </c>
+      <c r="H8">
+        <v>17.7</v>
+      </c>
+      <c r="I8">
+        <v>62.4</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.07618</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>82.00478</v>
+      </c>
+      <c r="E9">
+        <v>0.41738</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>17.4652</v>
+      </c>
+      <c r="H9">
+        <v>18.6</v>
+      </c>
+      <c r="I9">
+        <v>55.8</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0.10519</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4">
+        <v>46271.1511458333</v>
+      </c>
+      <c r="D10">
+        <v>81.98119</v>
+      </c>
+      <c r="E10">
+        <v>0.42209</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>17.47438</v>
+      </c>
+      <c r="H10">
+        <v>18.6</v>
+      </c>
+      <c r="I10">
+        <v>54</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.11507</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11">
+        <v>82.05141</v>
+      </c>
+      <c r="E11">
+        <v>0.42515</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>17.41678</v>
+      </c>
+      <c r="H11">
+        <v>15.4</v>
+      </c>
+      <c r="I11">
+        <v>60.4</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0.09907</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12">
+        <v>82.10519</v>
+      </c>
+      <c r="E12">
+        <v>0.42866</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>17.33673</v>
+      </c>
+      <c r="H12">
+        <v>16.8</v>
+      </c>
+      <c r="I12">
+        <v>63.7</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0.12137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13">
+        <v>82.03838</v>
+      </c>
+      <c r="E13">
+        <v>0.43886</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>17.32688</v>
+      </c>
+      <c r="H13">
+        <v>20.9</v>
+      </c>
+      <c r="I13">
+        <v>58.3</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0.18795</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14">
+        <v>81.9981</v>
+      </c>
+      <c r="E14">
+        <v>0.44273</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>17.36938</v>
+      </c>
+      <c r="H14">
+        <v>17.7</v>
+      </c>
+      <c r="I14">
+        <v>53.8</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0.18264</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15">
+        <v>81.99336</v>
+      </c>
+      <c r="E15">
+        <v>0.44352</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>17.35115</v>
+      </c>
+      <c r="H15">
+        <v>17.6</v>
+      </c>
+      <c r="I15">
+        <v>59.2</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0.20429</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16">
+        <v>81.99844</v>
+      </c>
+      <c r="E16">
+        <v>0.45164</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>17.32853</v>
+      </c>
+      <c r="H16">
+        <v>17</v>
+      </c>
+      <c r="I16">
+        <v>57.3</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0.21396</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17">
+        <v>81.96129</v>
+      </c>
+      <c r="E17">
+        <v>0.44445</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>17.35005</v>
+      </c>
+      <c r="H17">
+        <v>17.6</v>
+      </c>
+      <c r="I17">
+        <v>57.5</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0.23671</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18">
+        <v>81.98632</v>
+      </c>
+      <c r="E18">
+        <v>0.45563</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>17.29155</v>
+      </c>
+      <c r="H18">
+        <v>18.1</v>
+      </c>
+      <c r="I18">
+        <v>62</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0.25848</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19">
+        <v>81.98891</v>
+      </c>
+      <c r="E19">
+        <v>0.44233</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>17.32212</v>
+      </c>
+      <c r="H19">
+        <v>19.1</v>
+      </c>
+      <c r="I19">
+        <v>48.4</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0.23989</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20">
+        <v>81.39819</v>
+      </c>
+      <c r="E20">
+        <v>0.44434</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>17.40719</v>
+      </c>
+      <c r="H20">
+        <v>15</v>
+      </c>
+      <c r="I20">
+        <v>49</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0.74388</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21">
+        <v>81.55492</v>
+      </c>
+      <c r="E21">
+        <v>0.44413</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>17.47364</v>
+      </c>
+      <c r="H21">
+        <v>14.6</v>
+      </c>
+      <c r="I21">
+        <v>50.8</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0.52077</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22">
+        <v>81.68259</v>
+      </c>
+      <c r="E22">
+        <v>0.44189</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>17.43107</v>
+      </c>
+      <c r="H22">
+        <v>18.2</v>
+      </c>
+      <c r="I22">
+        <v>49.8</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0.43764</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23">
+        <v>81.86106</v>
+      </c>
+      <c r="E23">
+        <v>0.44188</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>17.38223</v>
+      </c>
+      <c r="H23">
+        <v>14.2</v>
+      </c>
+      <c r="I23">
+        <v>52.7</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0.30814</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
+        <v>46272.0146875</v>
+      </c>
       <c r="D24">
-        <v>81.99542</v>
+        <v>82.03464</v>
       </c>
       <c r="E24">
-        <v>0.39205</v>
+        <v>0.53176</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>17.56161</v>
+        <v>16.86531</v>
       </c>
       <c r="H24">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="I24">
-        <v>48</v>
+        <v>45.6</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0.04434</v>
+        <v>0.56199</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2288,32 +3785,32 @@
       <c r="B25">
         <v>2</v>
       </c>
-      <c r="C25" t="s">
-        <v>35</v>
+      <c r="C25" s="3">
+        <v>46272.0314467593</v>
       </c>
       <c r="D25">
-        <v>82.08538</v>
+        <v>81.95759</v>
       </c>
       <c r="E25">
-        <v>0.3996</v>
+        <v>0.52989</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>17.46044</v>
+        <v>16.95483</v>
       </c>
       <c r="H25">
         <v>18.1</v>
       </c>
       <c r="I25">
-        <v>62.9</v>
+        <v>43.3</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0.04647</v>
+        <v>0.55155</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2323,32 +3820,32 @@
       <c r="B26">
         <v>3</v>
       </c>
-      <c r="C26" t="s">
-        <v>36</v>
+      <c r="C26" s="3">
+        <v>46272.0481944444</v>
       </c>
       <c r="D26">
-        <v>82.05372</v>
+        <v>81.94735</v>
       </c>
       <c r="E26">
-        <v>0.41003</v>
+        <v>0.5258</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>17.448</v>
+        <v>16.97825</v>
       </c>
       <c r="H26">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="I26">
-        <v>61</v>
+        <v>37.5</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0.07048</v>
+        <v>0.54316</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2358,32 +3855,32 @@
       <c r="B27">
         <v>4</v>
       </c>
-      <c r="C27" t="s">
-        <v>37</v>
+      <c r="C27" s="3">
+        <v>46272.0649421296</v>
       </c>
       <c r="D27">
-        <v>82.08195</v>
+        <v>81.96411</v>
       </c>
       <c r="E27">
-        <v>0.40991</v>
+        <v>0.5231</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>17.45259</v>
+        <v>16.96215</v>
       </c>
       <c r="H27">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="I27">
-        <v>63.4</v>
+        <v>40.9</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0.04748</v>
+        <v>0.54483</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2393,32 +3890,32 @@
       <c r="B28">
         <v>5</v>
       </c>
-      <c r="C28" t="s">
-        <v>38</v>
+      <c r="C28" s="3">
+        <v>46272.0816898148</v>
       </c>
       <c r="D28">
-        <v>82.05914</v>
+        <v>81.98873</v>
       </c>
       <c r="E28">
-        <v>0.41312</v>
+        <v>0.52013</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>17.45248</v>
+        <v>16.93758</v>
       </c>
       <c r="H28">
-        <v>17.9</v>
+        <v>17.6</v>
       </c>
       <c r="I28">
-        <v>60.1</v>
+        <v>39.1</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0.06747</v>
+        <v>0.54788</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2428,32 +3925,32 @@
       <c r="B29">
         <v>6</v>
       </c>
-      <c r="C29" t="s">
-        <v>39</v>
+      <c r="C29" s="3">
+        <v>46272.0984375</v>
       </c>
       <c r="D29">
-        <v>82.03971</v>
+        <v>82.04629</v>
       </c>
       <c r="E29">
-        <v>0.41467</v>
+        <v>0.51959</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>17.47815</v>
+        <v>16.87651</v>
       </c>
       <c r="H29">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="I29">
-        <v>61.1</v>
+        <v>41.3</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0.05958</v>
+        <v>0.55171</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2463,32 +3960,32 @@
       <c r="B30">
         <v>7</v>
       </c>
-      <c r="C30" t="s">
-        <v>40</v>
+      <c r="C30" s="3">
+        <v>46272.1151736111</v>
       </c>
       <c r="D30">
-        <v>82.02074</v>
+        <v>82.08761</v>
       </c>
       <c r="E30">
-        <v>0.4145</v>
+        <v>0.52854</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>17.48058</v>
+        <v>16.8273</v>
       </c>
       <c r="H30">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="I30">
-        <v>62.4</v>
+        <v>38.9</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0.07618</v>
+        <v>0.55085</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2498,32 +3995,32 @@
       <c r="B31">
         <v>8</v>
       </c>
-      <c r="C31" t="s">
-        <v>41</v>
+      <c r="C31" s="3">
+        <v>46272.1319212963</v>
       </c>
       <c r="D31">
-        <v>82.00478</v>
+        <v>82.07238</v>
       </c>
       <c r="E31">
-        <v>0.41738</v>
+        <v>0.52982</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>17.4652</v>
+        <v>16.84721</v>
       </c>
       <c r="H31">
-        <v>18.6</v>
+        <v>17.4</v>
       </c>
       <c r="I31">
-        <v>55.8</v>
+        <v>42</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0.10519</v>
+        <v>0.54465</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2534,31 +4031,31 @@
         <v>9</v>
       </c>
       <c r="C32" s="3">
-        <v>46271.1511458333</v>
+        <v>46272.1486805556</v>
       </c>
       <c r="D32">
-        <v>81.98119</v>
+        <v>82.03977</v>
       </c>
       <c r="E32">
-        <v>0.42209</v>
+        <v>0.53135</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>17.47438</v>
+        <v>16.87885</v>
       </c>
       <c r="H32">
-        <v>18.6</v>
+        <v>17.8</v>
       </c>
       <c r="I32">
-        <v>54</v>
+        <v>41.5</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0.11507</v>
+        <v>0.54411</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2568,32 +4065,32 @@
       <c r="B33">
         <v>10</v>
       </c>
-      <c r="C33" t="s">
-        <v>42</v>
+      <c r="C33" s="3">
+        <v>46272.1654282407</v>
       </c>
       <c r="D33">
-        <v>82.05141</v>
+        <v>82.06491</v>
       </c>
       <c r="E33">
-        <v>0.42515</v>
+        <v>0.53347</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>17.41678</v>
+        <v>16.86681</v>
       </c>
       <c r="H33">
-        <v>15.4</v>
+        <v>18.1</v>
       </c>
       <c r="I33">
-        <v>60.4</v>
+        <v>40.2</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0.09907</v>
+        <v>0.52898</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2603,32 +4100,32 @@
       <c r="B34">
         <v>11</v>
       </c>
-      <c r="C34" t="s">
-        <v>43</v>
+      <c r="C34" s="3">
+        <v>46272.1821643518</v>
       </c>
       <c r="D34">
-        <v>82.10519</v>
+        <v>82.08781</v>
       </c>
       <c r="E34">
-        <v>0.42866</v>
+        <v>0.53345</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>17.33673</v>
+        <v>16.85033</v>
       </c>
       <c r="H34">
-        <v>16.8</v>
+        <v>18.5</v>
       </c>
       <c r="I34">
-        <v>63.7</v>
+        <v>38.9</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0.12137</v>
+        <v>0.52268</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2638,32 +4135,32 @@
       <c r="B35">
         <v>12</v>
       </c>
-      <c r="C35" t="s">
-        <v>44</v>
+      <c r="C35" s="3">
+        <v>46272.198900463</v>
       </c>
       <c r="D35">
-        <v>82.03838</v>
+        <v>82.12206</v>
       </c>
       <c r="E35">
-        <v>0.43886</v>
+        <v>0.53406</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>17.32688</v>
+        <v>16.81298</v>
       </c>
       <c r="H35">
-        <v>20.9</v>
+        <v>18.2</v>
       </c>
       <c r="I35">
-        <v>58.3</v>
+        <v>40</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0.18795</v>
+        <v>0.52507</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2673,32 +4170,32 @@
       <c r="B36">
         <v>13</v>
       </c>
-      <c r="C36" t="s">
-        <v>45</v>
+      <c r="C36" s="3">
+        <v>46272.2156365741</v>
       </c>
       <c r="D36">
-        <v>81.9981</v>
+        <v>82.20254</v>
       </c>
       <c r="E36">
-        <v>0.44273</v>
+        <v>0.53413</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>17.36938</v>
+        <v>16.72812</v>
       </c>
       <c r="H36">
-        <v>17.7</v>
+        <v>19</v>
       </c>
       <c r="I36">
-        <v>53.8</v>
+        <v>37.2</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0.18264</v>
+        <v>0.52959</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2708,32 +4205,32 @@
       <c r="B37">
         <v>14</v>
       </c>
-      <c r="C37" t="s">
-        <v>46</v>
+      <c r="C37" s="3">
+        <v>46272.2323726852</v>
       </c>
       <c r="D37">
-        <v>81.99336</v>
+        <v>82.22564</v>
       </c>
       <c r="E37">
-        <v>0.44352</v>
+        <v>0.53382</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>17.35115</v>
+        <v>16.71691</v>
       </c>
       <c r="H37">
-        <v>17.6</v>
+        <v>19.2</v>
       </c>
       <c r="I37">
-        <v>59.2</v>
+        <v>38.2</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0.20429</v>
+        <v>0.51789</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2743,32 +4240,32 @@
       <c r="B38">
         <v>15</v>
       </c>
-      <c r="C38" t="s">
-        <v>47</v>
+      <c r="C38" s="3">
+        <v>46272.2491203704</v>
       </c>
       <c r="D38">
-        <v>81.99844</v>
+        <v>82.26284</v>
       </c>
       <c r="E38">
-        <v>0.45164</v>
+        <v>0.53367</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>17.32853</v>
+        <v>16.70205</v>
       </c>
       <c r="H38">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="I38">
-        <v>57.3</v>
+        <v>38</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0.21396</v>
+        <v>0.4957</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2778,32 +4275,32 @@
       <c r="B39">
         <v>16</v>
       </c>
-      <c r="C39" t="s">
-        <v>48</v>
+      <c r="C39" s="3">
+        <v>46272.2658680556</v>
       </c>
       <c r="D39">
-        <v>81.96129</v>
+        <v>82.34222</v>
       </c>
       <c r="E39">
-        <v>0.44445</v>
+        <v>0.53803</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>17.35005</v>
+        <v>16.62043</v>
       </c>
       <c r="H39">
-        <v>17.6</v>
+        <v>19</v>
       </c>
       <c r="I39">
-        <v>57.5</v>
+        <v>39.2</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0.23671</v>
+        <v>0.4935</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2813,32 +4310,32 @@
       <c r="B40">
         <v>17</v>
       </c>
-      <c r="C40" t="s">
-        <v>49</v>
+      <c r="C40" s="3">
+        <v>46272.2826273148</v>
       </c>
       <c r="D40">
-        <v>81.98632</v>
+        <v>82.36739</v>
       </c>
       <c r="E40">
-        <v>0.45563</v>
+        <v>0.53946</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>17.29155</v>
+        <v>16.61173</v>
       </c>
       <c r="H40">
-        <v>18.1</v>
+        <v>19.5</v>
       </c>
       <c r="I40">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0.25848</v>
+        <v>0.47547</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2848,32 +4345,32 @@
       <c r="B41">
         <v>18</v>
       </c>
-      <c r="C41" t="s">
-        <v>50</v>
+      <c r="C41" s="3">
+        <v>46272.2993865741</v>
       </c>
       <c r="D41">
-        <v>81.98891</v>
+        <v>82.37072</v>
       </c>
       <c r="E41">
-        <v>0.44233</v>
+        <v>0.53874</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>17.32212</v>
+        <v>16.63857</v>
       </c>
       <c r="H41">
         <v>19.1</v>
       </c>
       <c r="I41">
-        <v>48.4</v>
+        <v>39.8</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0.23989</v>
+        <v>0.44608</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2883,911 +4380,1528 @@
       <c r="B42">
         <v>19</v>
       </c>
-      <c r="C42" t="s">
-        <v>51</v>
+      <c r="C42" s="3">
+        <v>46272.3161458333</v>
       </c>
       <c r="D42">
-        <v>81.39819</v>
+        <v>82.33875</v>
       </c>
       <c r="E42">
-        <v>0.44434</v>
+        <v>0.53514</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>17.40719</v>
+        <v>16.69898</v>
       </c>
       <c r="H42">
+        <v>18.2</v>
+      </c>
+      <c r="I42">
+        <v>33.7</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0.42195</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:C23">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="23.575" customWidth="1"/>
+    <col min="2" max="2" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="24.125" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="10.375" customWidth="1"/>
+    <col min="7" max="7" width="11.625" customWidth="1"/>
+    <col min="11" max="11" width="11.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2">
+        <v>79.61612</v>
+      </c>
+      <c r="E2">
+        <v>0.1359</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>20.24152</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>12</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.00526</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3">
+        <v>79.60239</v>
+      </c>
+      <c r="E3">
+        <v>0.14297</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>20.24461</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>5.5</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.00947</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4">
+        <v>79.60741</v>
+      </c>
+      <c r="E4">
+        <v>0.13869</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>20.24417</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>13.2</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.00841</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5">
+        <v>79.60363</v>
+      </c>
+      <c r="E5">
+        <v>0.14241</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>20.24653</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>10.7</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.00637</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>79.60885</v>
+      </c>
+      <c r="E6">
+        <v>0.14279</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>20.23795</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>16.6</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0.00876</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7">
+        <v>79.60531</v>
+      </c>
+      <c r="E7">
+        <v>0.14508</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>20.23831</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>13.8</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.00992</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8">
+        <v>79.61531</v>
+      </c>
+      <c r="E8">
+        <v>0.1463</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>20.22792</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>5.6</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.00991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9">
+        <v>79.61908</v>
+      </c>
+      <c r="E9">
+        <v>0.14954</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>20.21532</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>12.6</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0.0148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10">
+        <v>79.61739</v>
+      </c>
+      <c r="E10">
+        <v>0.15143</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>20.21877</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>16.6</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.01074</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11">
+        <v>79.63747</v>
+      </c>
+      <c r="E11">
+        <v>0.14502</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>20.19955</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>21.4</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0.01581</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12">
+        <v>79.65502</v>
+      </c>
+      <c r="E12">
+        <v>0.14949</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>20.17608</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>14.1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13">
+        <v>79.64436</v>
+      </c>
+      <c r="E13">
+        <v>0.14558</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>20.19073</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0.1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0.01932</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14">
+        <v>79.65282</v>
+      </c>
+      <c r="E14">
+        <v>0.12027</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>20.20247</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>18.9</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0.02255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15">
+        <v>79.6329</v>
+      </c>
+      <c r="E15">
+        <v>0.1557</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>20.18617</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>7.8</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0.02446</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16">
         <v>15</v>
       </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16">
+        <v>79.65955</v>
+      </c>
+      <c r="E16">
+        <v>0.15199</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>20.16149</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>5.1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0.02646</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17">
+        <v>79.61407</v>
+      </c>
+      <c r="E17">
+        <v>0.15021</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>20.1977</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0.03803</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18">
+        <v>79.62184</v>
+      </c>
+      <c r="E18">
+        <v>0.14727</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>20.19237</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>12</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0.03733</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19">
+        <v>79.62681</v>
+      </c>
+      <c r="E19">
+        <v>0.1443</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>20.18239</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>15.2</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0.04498</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20">
+        <v>79.57635</v>
+      </c>
+      <c r="E20">
+        <v>0.14385</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>20.19322</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0.08657</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21">
+        <v>79.57614</v>
+      </c>
+      <c r="E21">
+        <v>0.14019</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>20.20497</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0.8</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0.07862</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22">
+        <v>79.59612</v>
+      </c>
+      <c r="E22">
+        <v>0.14104</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>20.19971</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>1.5</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0.06298</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23">
+        <v>79.58314</v>
+      </c>
+      <c r="E23">
+        <v>0.14392</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>20.21043</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>3.5</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0.06218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
+        <v>46272.0202777778</v>
+      </c>
+      <c r="D24">
+        <v>79.7985</v>
+      </c>
+      <c r="E24">
+        <v>0.10351</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>20.01461</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0.08337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3">
+        <v>46272.037037037</v>
+      </c>
+      <c r="D25">
+        <v>79.80434</v>
+      </c>
+      <c r="E25">
+        <v>0.10878</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>20.00454</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>3.4</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3">
+        <v>46272.0537731481</v>
+      </c>
+      <c r="D26">
+        <v>79.79906</v>
+      </c>
+      <c r="E26">
+        <v>0.10692</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>20.01238</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0.08164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3">
+        <v>46272.0705208333</v>
+      </c>
+      <c r="D27">
+        <v>79.90004</v>
+      </c>
+      <c r="E27">
+        <v>0.13341</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>19.88526</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>4.5</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0.08084</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3">
+        <v>46272.0872685185</v>
+      </c>
+      <c r="D28">
+        <v>79.82239</v>
+      </c>
+      <c r="E28">
+        <v>0.11098</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>19.98586</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0.08077</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29" s="3">
+        <v>46272.1040162037</v>
+      </c>
+      <c r="D29">
+        <v>79.81213</v>
+      </c>
+      <c r="E29">
+        <v>0.11179</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>19.99172</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>4.5</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0.0839</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30" s="3">
+        <v>46272.1207638889</v>
+      </c>
+      <c r="D30">
+        <v>79.82423</v>
+      </c>
+      <c r="E30">
+        <v>0.10778</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>19.98439</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0.0836</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31" s="3">
+        <v>46272.1375</v>
+      </c>
+      <c r="D31">
+        <v>79.83891</v>
+      </c>
+      <c r="E31">
+        <v>0.10992</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>19.96835</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0.08282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3">
+        <v>46272.1542592593</v>
+      </c>
+      <c r="D32">
+        <v>79.85841</v>
+      </c>
+      <c r="E32">
+        <v>0.10282</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>19.95703</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0.08175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3">
+        <v>46272.1710069444</v>
+      </c>
+      <c r="D33">
+        <v>79.86067</v>
+      </c>
+      <c r="E33">
+        <v>0.10665</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>19.951</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0.08168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34">
+        <v>11</v>
+      </c>
+      <c r="C34" s="3">
+        <v>46272.1877430556</v>
+      </c>
+      <c r="D34">
+        <v>79.85664</v>
+      </c>
+      <c r="E34">
+        <v>0.10777</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>19.95532</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0.08027</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35">
+        <v>12</v>
+      </c>
+      <c r="C35" s="3">
+        <v>46272.2044791667</v>
+      </c>
+      <c r="D35">
+        <v>79.86595</v>
+      </c>
+      <c r="E35">
+        <v>0.10548</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>19.94613</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0.08243</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36">
+        <v>13</v>
+      </c>
+      <c r="C36" s="3">
+        <v>46272.2212268518</v>
+      </c>
+      <c r="D36">
+        <v>79.87371</v>
+      </c>
+      <c r="E36">
+        <v>0.10507</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>19.94132</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0.0799</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37">
+        <v>14</v>
+      </c>
+      <c r="C37" s="3">
+        <v>46272.237962963</v>
+      </c>
+      <c r="D37">
+        <v>79.89536</v>
+      </c>
+      <c r="E37">
+        <v>0.11716</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>19.91037</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>3.6</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0.07675</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38">
+        <v>15</v>
+      </c>
+      <c r="C38" s="3">
+        <v>46272.2546990741</v>
+      </c>
+      <c r="D38">
+        <v>79.90434</v>
+      </c>
+      <c r="E38">
+        <v>0.10893</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>19.91112</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>2.4</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0.07537</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39">
+        <v>16</v>
+      </c>
+      <c r="C39" s="3">
+        <v>46272.2714583333</v>
+      </c>
+      <c r="D39">
+        <v>79.89047</v>
+      </c>
+      <c r="E39">
+        <v>0.10396</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>19.93139</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>5.1</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0.07366</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40">
+        <v>17</v>
+      </c>
+      <c r="C40" s="3">
+        <v>46272.2882175926</v>
+      </c>
+      <c r="D40">
+        <v>79.89756</v>
+      </c>
+      <c r="E40">
+        <v>0.0978</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>19.93586</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>2.6</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0.06852</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41">
+        <v>18</v>
+      </c>
+      <c r="C41" s="3">
+        <v>46272.3049652778</v>
+      </c>
+      <c r="D41">
+        <v>79.91561</v>
+      </c>
+      <c r="E41">
+        <v>0.09882</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>19.91514</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>1.3</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0.0703</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42">
+        <v>19</v>
+      </c>
+      <c r="C42" s="3">
+        <v>46272.3217361111</v>
+      </c>
+      <c r="D42">
+        <v>79.93674</v>
+      </c>
+      <c r="E42">
+        <v>0.09439</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>19.9024</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
       <c r="I42">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0.74388</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43">
-        <v>20</v>
-      </c>
-      <c r="C43" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43">
-        <v>81.55492</v>
-      </c>
-      <c r="E43">
-        <v>0.44413</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>17.47364</v>
-      </c>
-      <c r="H43">
-        <v>14.6</v>
-      </c>
-      <c r="I43">
-        <v>50.8</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0.52077</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" t="s">
-        <v>33</v>
-      </c>
-      <c r="B44">
-        <v>21</v>
-      </c>
-      <c r="C44" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44">
-        <v>81.68259</v>
-      </c>
-      <c r="E44">
-        <v>0.44189</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>17.43107</v>
-      </c>
-      <c r="H44">
-        <v>18.2</v>
-      </c>
-      <c r="I44">
-        <v>49.8</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0.43764</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45">
-        <v>22</v>
-      </c>
-      <c r="C45" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45">
-        <v>81.86106</v>
-      </c>
-      <c r="E45">
-        <v>0.44188</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>17.38223</v>
-      </c>
-      <c r="H45">
-        <v>14.2</v>
-      </c>
-      <c r="I45">
-        <v>52.7</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0.30814</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>56</v>
-      </c>
-      <c r="D46">
-        <v>79.61612</v>
-      </c>
-      <c r="E46">
-        <v>0.1359</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>20.24152</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>12</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0.00526</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47">
-        <v>2</v>
-      </c>
-      <c r="C47" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47">
-        <v>79.60239</v>
-      </c>
-      <c r="E47">
-        <v>0.14297</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>20.24461</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>5.5</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0.00947</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>58</v>
-      </c>
-      <c r="D48">
-        <v>79.60741</v>
-      </c>
-      <c r="E48">
-        <v>0.13869</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>20.24417</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>13.2</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0.00841</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49">
-        <v>4</v>
-      </c>
-      <c r="C49" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49">
-        <v>79.60363</v>
-      </c>
-      <c r="E49">
-        <v>0.14241</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>20.24653</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>10.7</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0.00637</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50">
-        <v>5</v>
-      </c>
-      <c r="C50" t="s">
-        <v>60</v>
-      </c>
-      <c r="D50">
-        <v>79.60885</v>
-      </c>
-      <c r="E50">
-        <v>0.14279</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>20.23795</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>16.6</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0.00876</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" t="s">
-        <v>55</v>
-      </c>
-      <c r="B51">
-        <v>6</v>
-      </c>
-      <c r="C51" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51">
-        <v>79.60531</v>
-      </c>
-      <c r="E51">
-        <v>0.14508</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>20.23831</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>13.8</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0.00992</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52">
-        <v>7</v>
-      </c>
-      <c r="C52" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52">
-        <v>79.61531</v>
-      </c>
-      <c r="E52">
-        <v>0.1463</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>20.22792</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>5.6</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0.00991</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53">
-        <v>8</v>
-      </c>
-      <c r="C53" t="s">
-        <v>63</v>
-      </c>
-      <c r="D53">
-        <v>79.61908</v>
-      </c>
-      <c r="E53">
-        <v>0.14954</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>20.21532</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>12.6</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0.0148</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54">
-        <v>9</v>
-      </c>
-      <c r="C54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D54">
-        <v>79.61739</v>
-      </c>
-      <c r="E54">
-        <v>0.15143</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>20.21877</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54">
-        <v>16.6</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0.01074</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55">
-        <v>10</v>
-      </c>
-      <c r="C55" t="s">
-        <v>65</v>
-      </c>
-      <c r="D55">
-        <v>79.63747</v>
-      </c>
-      <c r="E55">
-        <v>0.14502</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>20.19955</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>21.4</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0.01581</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56">
-        <v>11</v>
-      </c>
-      <c r="C56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56">
-        <v>79.65502</v>
-      </c>
-      <c r="E56">
-        <v>0.14949</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>20.17608</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>14.1</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>0.018</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
-      <c r="A57" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57">
-        <v>12</v>
-      </c>
-      <c r="C57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57">
-        <v>79.64436</v>
-      </c>
-      <c r="E57">
-        <v>0.14558</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>20.19073</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0.1</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>0.01932</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="A58" t="s">
-        <v>55</v>
-      </c>
-      <c r="B58">
-        <v>13</v>
-      </c>
-      <c r="C58" t="s">
-        <v>68</v>
-      </c>
-      <c r="D58">
-        <v>79.65282</v>
-      </c>
-      <c r="E58">
-        <v>0.12027</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>20.20247</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>18.9</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>0.02255</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59">
-        <v>14</v>
-      </c>
-      <c r="C59" t="s">
-        <v>69</v>
-      </c>
-      <c r="D59">
-        <v>79.6329</v>
-      </c>
-      <c r="E59">
-        <v>0.1557</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>20.18617</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>7.8</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>0.02446</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
-      <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60">
-        <v>15</v>
-      </c>
-      <c r="C60" t="s">
-        <v>70</v>
-      </c>
-      <c r="D60">
-        <v>79.65955</v>
-      </c>
-      <c r="E60">
-        <v>0.15199</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>20.16149</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
-      <c r="I60">
-        <v>5.1</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <v>0.02646</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61">
-        <v>16</v>
-      </c>
-      <c r="C61" t="s">
-        <v>71</v>
-      </c>
-      <c r="D61">
-        <v>79.61407</v>
-      </c>
-      <c r="E61">
-        <v>0.15021</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>20.1977</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>0.03803</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
-      <c r="A62" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62">
-        <v>17</v>
-      </c>
-      <c r="C62" t="s">
-        <v>72</v>
-      </c>
-      <c r="D62">
-        <v>79.62184</v>
-      </c>
-      <c r="E62">
-        <v>0.14727</v>
-      </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <v>20.19237</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>12</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>0.03733</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
-      <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63">
-        <v>18</v>
-      </c>
-      <c r="C63" t="s">
-        <v>73</v>
-      </c>
-      <c r="D63">
-        <v>79.62681</v>
-      </c>
-      <c r="E63">
-        <v>0.1443</v>
-      </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-      <c r="G63">
-        <v>20.18239</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>15.2</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0.04498</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="A64" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64">
-        <v>19</v>
-      </c>
-      <c r="C64" t="s">
-        <v>74</v>
-      </c>
-      <c r="D64">
-        <v>79.57635</v>
-      </c>
-      <c r="E64">
-        <v>0.14385</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64">
-        <v>20.19322</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0.08657</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65">
-        <v>20</v>
-      </c>
-      <c r="C65" t="s">
-        <v>75</v>
-      </c>
-      <c r="D65">
-        <v>79.57614</v>
-      </c>
-      <c r="E65">
-        <v>0.14019</v>
-      </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <v>20.20497</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0.8</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0.07862</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
-      <c r="A66" t="s">
-        <v>55</v>
-      </c>
-      <c r="B66">
-        <v>21</v>
-      </c>
-      <c r="C66" t="s">
-        <v>76</v>
-      </c>
-      <c r="D66">
-        <v>79.59612</v>
-      </c>
-      <c r="E66">
-        <v>0.14104</v>
-      </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66">
-        <v>20.19971</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>1.5</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0.06298</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
-      <c r="A67" t="s">
-        <v>55</v>
-      </c>
-      <c r="B67">
-        <v>22</v>
-      </c>
-      <c r="C67" t="s">
-        <v>77</v>
-      </c>
-      <c r="D67">
-        <v>79.58314</v>
-      </c>
-      <c r="E67">
-        <v>0.14392</v>
-      </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <v>20.21043</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>3.5</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0.06218</v>
+        <v>0.06647</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C67">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cfdata.xlsx
+++ b/cfdata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" activeTab="2"/>
+    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="12802采空区" sheetId="1" r:id="rId1"/>
